--- a/Data/Excel/pcr-data-mix.xlsx
+++ b/Data/Excel/pcr-data-mix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/cjm423_cornell_edu/Documents/study-1-march25/MIX/Data/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="930" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D30DCBB-1237-47DA-B187-317DCA48C6B0}"/>
+  <xr:revisionPtr revIDLastSave="1017" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E4AD4F-C410-46EC-BC77-D2F19A2DED46}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="26">
   <si>
     <t>Tissue</t>
   </si>
@@ -112,12 +112,18 @@
   <si>
     <t>Rep2</t>
   </si>
+  <si>
+    <t>MyoG</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###0.00;\-###0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +136,10 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.25"/>
+      <name val="Microsoft Sans Serif"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,8 +162,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9608A0BB-4834-4C56-8996-87339C4A28ED}">
-  <dimension ref="A1:F625"/>
+  <dimension ref="A1:F664"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
@@ -13003,6 +13016,786 @@
         <v>25.75</v>
       </c>
     </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
+        <v>16</v>
+      </c>
+      <c r="B626" t="s">
+        <v>5</v>
+      </c>
+      <c r="C626">
+        <v>1</v>
+      </c>
+      <c r="D626" t="s">
+        <v>25</v>
+      </c>
+      <c r="E626" s="1">
+        <v>28.053165621050098</v>
+      </c>
+      <c r="F626" s="1">
+        <v>28.0857390978917</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>16</v>
+      </c>
+      <c r="B627" t="s">
+        <v>5</v>
+      </c>
+      <c r="C627">
+        <v>2</v>
+      </c>
+      <c r="D627" t="s">
+        <v>25</v>
+      </c>
+      <c r="E627" s="1">
+        <v>30.0503992850206</v>
+      </c>
+      <c r="F627" s="1">
+        <v>29.914640295490202</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>16</v>
+      </c>
+      <c r="B628" t="s">
+        <v>5</v>
+      </c>
+      <c r="C628">
+        <v>3</v>
+      </c>
+      <c r="D628" t="s">
+        <v>25</v>
+      </c>
+      <c r="E628" s="1">
+        <v>28.808130776376899</v>
+      </c>
+      <c r="F628" s="1">
+        <v>28.576923817220301</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
+        <v>16</v>
+      </c>
+      <c r="B629" t="s">
+        <v>5</v>
+      </c>
+      <c r="C629">
+        <v>4</v>
+      </c>
+      <c r="D629" t="s">
+        <v>25</v>
+      </c>
+      <c r="E629" s="1">
+        <v>28.284978647312801</v>
+      </c>
+      <c r="F629" s="1">
+        <v>27.3132014966417</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
+        <v>16</v>
+      </c>
+      <c r="B630" t="s">
+        <v>5</v>
+      </c>
+      <c r="C630">
+        <v>5</v>
+      </c>
+      <c r="D630" t="s">
+        <v>25</v>
+      </c>
+      <c r="E630" s="1">
+        <v>30.390326192228802</v>
+      </c>
+      <c r="F630" s="1">
+        <v>30.485760002632802</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
+        <v>16</v>
+      </c>
+      <c r="B631" t="s">
+        <v>5</v>
+      </c>
+      <c r="C631">
+        <v>6</v>
+      </c>
+      <c r="D631" t="s">
+        <v>25</v>
+      </c>
+      <c r="E631" s="1">
+        <v>29.053738371678801</v>
+      </c>
+      <c r="F631" s="1">
+        <v>29.515994767132401</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
+        <v>16</v>
+      </c>
+      <c r="B632" t="s">
+        <v>5</v>
+      </c>
+      <c r="C632">
+        <v>7</v>
+      </c>
+      <c r="D632" t="s">
+        <v>25</v>
+      </c>
+      <c r="E632" s="1">
+        <v>29.1718625422718</v>
+      </c>
+      <c r="F632" s="1">
+        <v>29.363604750268301</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
+        <v>16</v>
+      </c>
+      <c r="B633" t="s">
+        <v>5</v>
+      </c>
+      <c r="C633">
+        <v>8</v>
+      </c>
+      <c r="D633" t="s">
+        <v>25</v>
+      </c>
+      <c r="E633" s="1">
+        <v>28.992182255112901</v>
+      </c>
+      <c r="F633" s="1">
+        <v>29.415704724209</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
+        <v>16</v>
+      </c>
+      <c r="B634" t="s">
+        <v>7</v>
+      </c>
+      <c r="C634">
+        <v>1</v>
+      </c>
+      <c r="D634" t="s">
+        <v>25</v>
+      </c>
+      <c r="E634" s="1">
+        <v>29.762943796644201</v>
+      </c>
+      <c r="F634" s="1">
+        <v>30.124111744582098</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
+        <v>16</v>
+      </c>
+      <c r="B635" t="s">
+        <v>7</v>
+      </c>
+      <c r="C635">
+        <v>2</v>
+      </c>
+      <c r="D635" t="s">
+        <v>25</v>
+      </c>
+      <c r="E635" s="1">
+        <v>29.003592063641801</v>
+      </c>
+      <c r="F635" s="1">
+        <v>28.430701827647901</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
+        <v>16</v>
+      </c>
+      <c r="B636" t="s">
+        <v>7</v>
+      </c>
+      <c r="C636">
+        <v>3</v>
+      </c>
+      <c r="D636" t="s">
+        <v>25</v>
+      </c>
+      <c r="E636" s="1">
+        <v>29.5501513232619</v>
+      </c>
+      <c r="F636" s="1">
+        <v>30.608154623024401</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>16</v>
+      </c>
+      <c r="B637" t="s">
+        <v>7</v>
+      </c>
+      <c r="C637">
+        <v>4</v>
+      </c>
+      <c r="D637" t="s">
+        <v>25</v>
+      </c>
+      <c r="E637" s="1">
+        <v>33.136986705476403</v>
+      </c>
+      <c r="F637" s="1">
+        <v>32.630932094647903</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
+        <v>16</v>
+      </c>
+      <c r="B638" t="s">
+        <v>7</v>
+      </c>
+      <c r="C638">
+        <v>5</v>
+      </c>
+      <c r="D638" t="s">
+        <v>25</v>
+      </c>
+      <c r="E638" s="1">
+        <v>28.425990012226102</v>
+      </c>
+      <c r="F638" s="1">
+        <v>28.392550644951999</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>16</v>
+      </c>
+      <c r="B639" t="s">
+        <v>7</v>
+      </c>
+      <c r="C639">
+        <v>6</v>
+      </c>
+      <c r="D639" t="s">
+        <v>25</v>
+      </c>
+      <c r="E639" s="1">
+        <v>29.4907493719132</v>
+      </c>
+      <c r="F639" s="1">
+        <v>29.533848063526602</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>16</v>
+      </c>
+      <c r="B640" t="s">
+        <v>7</v>
+      </c>
+      <c r="C640">
+        <v>7</v>
+      </c>
+      <c r="D640" t="s">
+        <v>25</v>
+      </c>
+      <c r="E640" s="1">
+        <v>29.704909939280899</v>
+      </c>
+      <c r="F640" s="1">
+        <v>30.357917384956199</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>16</v>
+      </c>
+      <c r="B641" t="s">
+        <v>8</v>
+      </c>
+      <c r="C641">
+        <v>1</v>
+      </c>
+      <c r="D641" t="s">
+        <v>25</v>
+      </c>
+      <c r="E641" s="1">
+        <v>27.168407914522099</v>
+      </c>
+      <c r="F641" s="1">
+        <v>27.6536793442815</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>16</v>
+      </c>
+      <c r="B642" t="s">
+        <v>8</v>
+      </c>
+      <c r="C642">
+        <v>2</v>
+      </c>
+      <c r="D642" t="s">
+        <v>25</v>
+      </c>
+      <c r="E642" s="1">
+        <v>27.609675486490001</v>
+      </c>
+      <c r="F642" s="1">
+        <v>26.964926728312399</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>16</v>
+      </c>
+      <c r="B643" t="s">
+        <v>8</v>
+      </c>
+      <c r="C643">
+        <v>3</v>
+      </c>
+      <c r="D643" t="s">
+        <v>25</v>
+      </c>
+      <c r="E643" s="1">
+        <v>28.144459995911301</v>
+      </c>
+      <c r="F643" s="1">
+        <v>28.764965480241798</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>16</v>
+      </c>
+      <c r="B644" t="s">
+        <v>8</v>
+      </c>
+      <c r="C644">
+        <v>4</v>
+      </c>
+      <c r="D644" t="s">
+        <v>25</v>
+      </c>
+      <c r="E644" s="1">
+        <v>27.182718432696198</v>
+      </c>
+      <c r="F644" s="1">
+        <v>27.336956639467399</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
+        <v>16</v>
+      </c>
+      <c r="B645" t="s">
+        <v>8</v>
+      </c>
+      <c r="C645">
+        <v>5</v>
+      </c>
+      <c r="D645" t="s">
+        <v>25</v>
+      </c>
+      <c r="E645" s="1">
+        <v>27.918984886755499</v>
+      </c>
+      <c r="F645" s="1">
+        <v>28.173490594127699</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>16</v>
+      </c>
+      <c r="B646" t="s">
+        <v>8</v>
+      </c>
+      <c r="C646">
+        <v>6</v>
+      </c>
+      <c r="D646" t="s">
+        <v>25</v>
+      </c>
+      <c r="E646" s="1">
+        <v>28.891312906224702</v>
+      </c>
+      <c r="F646" s="1">
+        <v>29.148843631370099</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
+        <v>16</v>
+      </c>
+      <c r="B647" t="s">
+        <v>8</v>
+      </c>
+      <c r="C647">
+        <v>7</v>
+      </c>
+      <c r="D647" t="s">
+        <v>25</v>
+      </c>
+      <c r="E647" s="1">
+        <v>28.011845115892399</v>
+      </c>
+      <c r="F647" s="1">
+        <v>28.185080985237398</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>16</v>
+      </c>
+      <c r="B648" t="s">
+        <v>8</v>
+      </c>
+      <c r="C648">
+        <v>8</v>
+      </c>
+      <c r="D648" t="s">
+        <v>25</v>
+      </c>
+      <c r="E648" s="1">
+        <v>27.6476583637108</v>
+      </c>
+      <c r="F648" s="1">
+        <v>28.067250069473499</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>16</v>
+      </c>
+      <c r="B649" t="s">
+        <v>9</v>
+      </c>
+      <c r="C649">
+        <v>1</v>
+      </c>
+      <c r="D649" t="s">
+        <v>25</v>
+      </c>
+      <c r="E649" s="1">
+        <v>33.102216295024199</v>
+      </c>
+      <c r="F649" s="1">
+        <v>33.104510385428803</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>16</v>
+      </c>
+      <c r="B650" t="s">
+        <v>9</v>
+      </c>
+      <c r="C650">
+        <v>2</v>
+      </c>
+      <c r="D650" t="s">
+        <v>25</v>
+      </c>
+      <c r="E650" s="1">
+        <v>27.813685509001399</v>
+      </c>
+      <c r="F650" s="1">
+        <v>27.786019371039401</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>16</v>
+      </c>
+      <c r="B651" t="s">
+        <v>9</v>
+      </c>
+      <c r="C651">
+        <v>3</v>
+      </c>
+      <c r="D651" t="s">
+        <v>25</v>
+      </c>
+      <c r="E651" s="1">
+        <v>27.0002496869593</v>
+      </c>
+      <c r="F651" s="1">
+        <v>27.048263111997301</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>16</v>
+      </c>
+      <c r="B652" t="s">
+        <v>9</v>
+      </c>
+      <c r="C652">
+        <v>4</v>
+      </c>
+      <c r="D652" t="s">
+        <v>25</v>
+      </c>
+      <c r="E652" s="1">
+        <v>26.914111002612199</v>
+      </c>
+      <c r="F652" s="1">
+        <v>26.680127577512302</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
+        <v>16</v>
+      </c>
+      <c r="B653" t="s">
+        <v>9</v>
+      </c>
+      <c r="C653">
+        <v>5</v>
+      </c>
+      <c r="D653" t="s">
+        <v>25</v>
+      </c>
+      <c r="E653" s="1">
+        <v>26.219470282299099</v>
+      </c>
+      <c r="F653" s="1">
+        <v>26.061908314495899</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>16</v>
+      </c>
+      <c r="B654" t="s">
+        <v>9</v>
+      </c>
+      <c r="C654">
+        <v>6</v>
+      </c>
+      <c r="D654" t="s">
+        <v>25</v>
+      </c>
+      <c r="E654" s="1">
+        <v>26.713019766875899</v>
+      </c>
+      <c r="F654" s="1">
+        <v>26.591890124942001</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
+        <v>16</v>
+      </c>
+      <c r="B655" t="s">
+        <v>9</v>
+      </c>
+      <c r="C655">
+        <v>7</v>
+      </c>
+      <c r="D655" t="s">
+        <v>25</v>
+      </c>
+      <c r="E655" s="1">
+        <v>28.341086290718099</v>
+      </c>
+      <c r="F655" s="1">
+        <v>28.133909413643501</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>16</v>
+      </c>
+      <c r="B656" t="s">
+        <v>9</v>
+      </c>
+      <c r="C656">
+        <v>8</v>
+      </c>
+      <c r="D656" t="s">
+        <v>25</v>
+      </c>
+      <c r="E656" s="1">
+        <v>25.840218410083899</v>
+      </c>
+      <c r="F656" s="1">
+        <v>26.463865557737702</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>16</v>
+      </c>
+      <c r="B657" t="s">
+        <v>10</v>
+      </c>
+      <c r="C657">
+        <v>1</v>
+      </c>
+      <c r="D657" t="s">
+        <v>25</v>
+      </c>
+      <c r="E657" s="1">
+        <v>27.398366465647001</v>
+      </c>
+      <c r="F657" s="1">
+        <v>27.102292986943301</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>16</v>
+      </c>
+      <c r="B658" t="s">
+        <v>10</v>
+      </c>
+      <c r="C658">
+        <v>2</v>
+      </c>
+      <c r="D658" t="s">
+        <v>25</v>
+      </c>
+      <c r="E658" s="1">
+        <v>26.850115891102799</v>
+      </c>
+      <c r="F658" s="1">
+        <v>26.795560367619</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>16</v>
+      </c>
+      <c r="B659" t="s">
+        <v>10</v>
+      </c>
+      <c r="C659">
+        <v>3</v>
+      </c>
+      <c r="D659" t="s">
+        <v>25</v>
+      </c>
+      <c r="E659" s="1">
+        <v>26.556454031254798</v>
+      </c>
+      <c r="F659" s="1">
+        <v>26.438626892519199</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>16</v>
+      </c>
+      <c r="B660" t="s">
+        <v>10</v>
+      </c>
+      <c r="C660">
+        <v>4</v>
+      </c>
+      <c r="D660" t="s">
+        <v>25</v>
+      </c>
+      <c r="E660" s="1">
+        <v>26.295859854968199</v>
+      </c>
+      <c r="F660" s="1">
+        <v>26.315415922219699</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>16</v>
+      </c>
+      <c r="B661" t="s">
+        <v>10</v>
+      </c>
+      <c r="C661">
+        <v>5</v>
+      </c>
+      <c r="D661" t="s">
+        <v>25</v>
+      </c>
+      <c r="E661" s="1">
+        <v>26.448558098527801</v>
+      </c>
+      <c r="F661" s="1">
+        <v>26.341777016003</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A662" t="s">
+        <v>16</v>
+      </c>
+      <c r="B662" t="s">
+        <v>10</v>
+      </c>
+      <c r="C662">
+        <v>6</v>
+      </c>
+      <c r="D662" t="s">
+        <v>25</v>
+      </c>
+      <c r="E662" s="1">
+        <v>26.8968557141418</v>
+      </c>
+      <c r="F662" s="1">
+        <v>26.675821102362899</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A663" t="s">
+        <v>16</v>
+      </c>
+      <c r="B663" t="s">
+        <v>10</v>
+      </c>
+      <c r="C663">
+        <v>7</v>
+      </c>
+      <c r="D663" t="s">
+        <v>25</v>
+      </c>
+      <c r="E663" s="1">
+        <v>26.190511241868499</v>
+      </c>
+      <c r="F663" s="1">
+        <v>26.071947071713101</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A664" t="s">
+        <v>16</v>
+      </c>
+      <c r="B664" t="s">
+        <v>10</v>
+      </c>
+      <c r="C664">
+        <v>8</v>
+      </c>
+      <c r="D664" t="s">
+        <v>25</v>
+      </c>
+      <c r="E664" s="1">
+        <v>26.186975051831801</v>
+      </c>
+      <c r="F664" s="1">
+        <v>26.1776042433413</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/pcr-data-mix.xlsx
+++ b/Data/Excel/pcr-data-mix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/cjm423_cornell_edu/Documents/study-1-march25/MIX/Data/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1017" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65E4AD4F-C410-46EC-BC77-D2F19A2DED46}"/>
+  <xr:revisionPtr revIDLastSave="1026" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6C5628B-B529-4CB5-8FA3-009C2EE99236}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="22">
   <si>
     <t>Tissue</t>
   </si>
@@ -83,22 +83,7 @@
     <t>Colon</t>
   </si>
   <si>
-    <t>mTOR</t>
-  </si>
-  <si>
-    <t>Pectoral</t>
-  </si>
-  <si>
     <t>Liver</t>
-  </si>
-  <si>
-    <t>MyoD</t>
-  </si>
-  <si>
-    <t>MyHC1</t>
-  </si>
-  <si>
-    <t>MyHC2a</t>
   </si>
   <si>
     <t>PRAAK1</t>
@@ -113,17 +98,17 @@
     <t>Rep2</t>
   </si>
   <si>
-    <t>MyoG</t>
+    <t>PPARg</t>
+  </si>
+  <si>
+    <t>DGAT2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###0.00;\-###0.00"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,10 +121,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.25"/>
-      <name val="Microsoft Sans Serif"/>
     </font>
   </fonts>
   <fills count="2">
@@ -162,11 +143,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9608A0BB-4834-4C56-8996-87339C4A28ED}">
-  <dimension ref="A1:F664"/>
+  <dimension ref="A1:F508"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
@@ -530,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -6778,7 +6756,7 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B314" t="s">
         <v>5</v>
@@ -6787,18 +6765,18 @@
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E314">
-        <v>25.56</v>
+        <v>20.07</v>
       </c>
       <c r="F314">
-        <v>25.24</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B315" t="s">
         <v>5</v>
@@ -6807,18 +6785,18 @@
         <v>2</v>
       </c>
       <c r="D315" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E315">
-        <v>26.12</v>
+        <v>20.27</v>
       </c>
       <c r="F315">
-        <v>25.4</v>
+        <v>20.420000000000002</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B316" t="s">
         <v>5</v>
@@ -6827,18 +6805,18 @@
         <v>3</v>
       </c>
       <c r="D316" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E316">
-        <v>24.88</v>
+        <v>19.22</v>
       </c>
       <c r="F316">
-        <v>24.34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B317" t="s">
         <v>5</v>
@@ -6847,18 +6825,18 @@
         <v>4</v>
       </c>
       <c r="D317" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E317">
-        <v>23.81</v>
+        <v>18.86</v>
       </c>
       <c r="F317">
-        <v>23.47</v>
+        <v>19.260000000000002</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B318" t="s">
         <v>5</v>
@@ -6867,18 +6845,18 @@
         <v>5</v>
       </c>
       <c r="D318" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E318">
-        <v>28.04</v>
+        <v>19.25</v>
       </c>
       <c r="F318">
-        <v>27.53</v>
+        <v>19.059999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B319" t="s">
         <v>5</v>
@@ -6887,18 +6865,18 @@
         <v>6</v>
       </c>
       <c r="D319" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E319">
-        <v>22.9</v>
+        <v>19.29</v>
       </c>
       <c r="F319">
-        <v>23.69</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B320" t="s">
         <v>5</v>
@@ -6907,18 +6885,18 @@
         <v>7</v>
       </c>
       <c r="D320" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E320">
-        <v>25.85</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="F320">
-        <v>25.97</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B321" t="s">
         <v>5</v>
@@ -6927,18 +6905,18 @@
         <v>8</v>
       </c>
       <c r="D321" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E321">
-        <v>26.26</v>
+        <v>18.29</v>
       </c>
       <c r="F321">
-        <v>25.33</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B322" t="s">
         <v>7</v>
@@ -6947,18 +6925,18 @@
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E322">
-        <v>26.53</v>
+        <v>19.75</v>
       </c>
       <c r="F322">
-        <v>25.52</v>
+        <v>19.940000000000001</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B323" t="s">
         <v>7</v>
@@ -6967,18 +6945,18 @@
         <v>2</v>
       </c>
       <c r="D323" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E323">
-        <v>25.61</v>
+        <v>20.8</v>
       </c>
       <c r="F323">
-        <v>24.97</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B324" t="s">
         <v>7</v>
@@ -6987,18 +6965,18 @@
         <v>3</v>
       </c>
       <c r="D324" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E324">
-        <v>26.17</v>
+        <v>19.77</v>
       </c>
       <c r="F324">
-        <v>26.62</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B325" t="s">
         <v>7</v>
@@ -7007,18 +6985,18 @@
         <v>4</v>
       </c>
       <c r="D325" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E325">
-        <v>26.54</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="F325">
-        <v>26.4</v>
+        <v>19.760000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B326" t="s">
         <v>7</v>
@@ -7027,18 +7005,18 @@
         <v>5</v>
       </c>
       <c r="D326" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E326">
-        <v>25.67</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="F326">
-        <v>26.01</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B327" t="s">
         <v>7</v>
@@ -7047,18 +7025,18 @@
         <v>6</v>
       </c>
       <c r="D327" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E327">
-        <v>26.39</v>
+        <v>21.21</v>
       </c>
       <c r="F327">
-        <v>26.12</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B328" t="s">
         <v>7</v>
@@ -7067,18 +7045,18 @@
         <v>7</v>
       </c>
       <c r="D328" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E328">
-        <v>26.9</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="F328">
-        <v>26.43</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B329" t="s">
         <v>8</v>
@@ -7087,18 +7065,18 @@
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E329">
-        <v>24.86</v>
+        <v>21</v>
       </c>
       <c r="F329">
-        <v>24.86</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B330" t="s">
         <v>8</v>
@@ -7107,18 +7085,18 @@
         <v>2</v>
       </c>
       <c r="D330" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E330">
-        <v>25.07</v>
+        <v>20.43</v>
       </c>
       <c r="F330">
-        <v>25.35</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B331" t="s">
         <v>8</v>
@@ -7127,18 +7105,18 @@
         <v>3</v>
       </c>
       <c r="D331" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E331">
-        <v>25.26</v>
+        <v>20.25</v>
       </c>
       <c r="F331">
-        <v>25.06</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B332" t="s">
         <v>8</v>
@@ -7147,18 +7125,18 @@
         <v>4</v>
       </c>
       <c r="D332" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E332">
-        <v>25.67</v>
+        <v>21.82</v>
       </c>
       <c r="F332">
-        <v>25.34</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B333" t="s">
         <v>8</v>
@@ -7167,18 +7145,18 @@
         <v>5</v>
       </c>
       <c r="D333" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E333">
-        <v>24.94</v>
+        <v>20.14</v>
       </c>
       <c r="F333">
-        <v>24.86</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B334" t="s">
         <v>8</v>
@@ -7187,18 +7165,18 @@
         <v>6</v>
       </c>
       <c r="D334" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E334">
-        <v>25.02</v>
+        <v>21.4</v>
       </c>
       <c r="F334">
-        <v>25.66</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B335" t="s">
         <v>8</v>
@@ -7207,18 +7185,18 @@
         <v>7</v>
       </c>
       <c r="D335" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E335">
-        <v>24</v>
+        <v>20.48</v>
       </c>
       <c r="F335">
-        <v>24.65</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B336" t="s">
         <v>8</v>
@@ -7227,18 +7205,18 @@
         <v>8</v>
       </c>
       <c r="D336" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E336">
-        <v>22.97</v>
+        <v>19.260000000000002</v>
       </c>
       <c r="F336">
-        <v>23.57</v>
+        <v>19.850000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B337" t="s">
         <v>9</v>
@@ -7247,18 +7225,18 @@
         <v>1</v>
       </c>
       <c r="D337" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E337">
-        <v>24.29</v>
+        <v>20.64</v>
       </c>
       <c r="F337">
-        <v>23.7</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B338" t="s">
         <v>9</v>
@@ -7267,18 +7245,18 @@
         <v>2</v>
       </c>
       <c r="D338" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E338">
-        <v>25.41</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="F338">
-        <v>24.84</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B339" t="s">
         <v>9</v>
@@ -7287,18 +7265,18 @@
         <v>3</v>
       </c>
       <c r="D339" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E339">
-        <v>25.29</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="F339">
-        <v>25.63</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B340" t="s">
         <v>9</v>
@@ -7307,18 +7285,18 @@
         <v>4</v>
       </c>
       <c r="D340" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E340">
-        <v>24.82</v>
+        <v>19.89</v>
       </c>
       <c r="F340">
-        <v>24.42</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B341" t="s">
         <v>9</v>
@@ -7327,18 +7305,18 @@
         <v>5</v>
       </c>
       <c r="D341" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E341">
-        <v>22.58</v>
+        <v>20.81</v>
       </c>
       <c r="F341">
-        <v>22.77</v>
+        <v>20.190000000000001</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B342" t="s">
         <v>9</v>
@@ -7347,18 +7325,18 @@
         <v>6</v>
       </c>
       <c r="D342" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E342">
-        <v>24.45</v>
+        <v>20.21</v>
       </c>
       <c r="F342">
-        <v>24.75</v>
+        <v>20.260000000000002</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B343" t="s">
         <v>9</v>
@@ -7367,18 +7345,18 @@
         <v>7</v>
       </c>
       <c r="D343" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E343">
-        <v>26.07</v>
+        <v>20.21</v>
       </c>
       <c r="F343">
-        <v>26.42</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B344" t="s">
         <v>9</v>
@@ -7387,18 +7365,18 @@
         <v>8</v>
       </c>
       <c r="D344" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E344">
-        <v>24.62</v>
+        <v>20.79</v>
       </c>
       <c r="F344">
-        <v>24.65</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B345" t="s">
         <v>10</v>
@@ -7407,18 +7385,18 @@
         <v>1</v>
       </c>
       <c r="D345" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E345">
-        <v>25.83</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="F345">
-        <v>25.86</v>
+        <v>19.510000000000002</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B346" t="s">
         <v>10</v>
@@ -7427,18 +7405,18 @@
         <v>2</v>
       </c>
       <c r="D346" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E346">
-        <v>24.32</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F346">
-        <v>24.35</v>
+        <v>19.239999999999998</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B347" t="s">
         <v>10</v>
@@ -7447,18 +7425,18 @@
         <v>3</v>
       </c>
       <c r="D347" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E347">
-        <v>24</v>
+        <v>20.66</v>
       </c>
       <c r="F347">
-        <v>23.61</v>
+        <v>20.190000000000001</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B348" t="s">
         <v>10</v>
@@ -7467,18 +7445,18 @@
         <v>4</v>
       </c>
       <c r="D348" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E348">
-        <v>24.46</v>
+        <v>20.2</v>
       </c>
       <c r="F348">
-        <v>24.46</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B349" t="s">
         <v>10</v>
@@ -7487,18 +7465,18 @@
         <v>5</v>
       </c>
       <c r="D349" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E349">
-        <v>25.22</v>
+        <v>20.22</v>
       </c>
       <c r="F349">
-        <v>25.39</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B350" t="s">
         <v>10</v>
@@ -7507,18 +7485,18 @@
         <v>6</v>
       </c>
       <c r="D350" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E350">
-        <v>25.41</v>
+        <v>21.97</v>
       </c>
       <c r="F350">
-        <v>25.09</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B351" t="s">
         <v>10</v>
@@ -7527,18 +7505,18 @@
         <v>7</v>
       </c>
       <c r="D351" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E351">
-        <v>23.61</v>
+        <v>20.23</v>
       </c>
       <c r="F351">
-        <v>24.2</v>
+        <v>20.440000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B352" t="s">
         <v>10</v>
@@ -7547,18 +7525,18 @@
         <v>8</v>
       </c>
       <c r="D352" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E352">
-        <v>25.65</v>
+        <v>20.67</v>
       </c>
       <c r="F352">
-        <v>25.27</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B353" t="s">
         <v>5</v>
@@ -7567,18 +7545,18 @@
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E353">
-        <v>26.71</v>
+        <v>27.88</v>
       </c>
       <c r="F353">
-        <v>27.06</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B354" t="s">
         <v>5</v>
@@ -7587,18 +7565,18 @@
         <v>2</v>
       </c>
       <c r="D354" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E354">
-        <v>26.77</v>
+        <v>26.78</v>
       </c>
       <c r="F354">
-        <v>27.03</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B355" t="s">
         <v>5</v>
@@ -7607,118 +7585,118 @@
         <v>3</v>
       </c>
       <c r="D355" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E355">
-        <v>27.3</v>
+        <v>26.03</v>
       </c>
       <c r="F355">
-        <v>27.21</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
+        <v>15</v>
+      </c>
+      <c r="B356" t="s">
+        <v>5</v>
+      </c>
+      <c r="C356">
+        <v>4</v>
+      </c>
+      <c r="D356" t="s">
         <v>16</v>
       </c>
-      <c r="B356" t="s">
-        <v>5</v>
-      </c>
-      <c r="C356">
-        <v>4</v>
-      </c>
-      <c r="D356" t="s">
-        <v>6</v>
-      </c>
       <c r="E356">
-        <v>24.89</v>
+        <v>25.41</v>
       </c>
       <c r="F356">
-        <v>24.07</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
+        <v>15</v>
+      </c>
+      <c r="B357" t="s">
+        <v>5</v>
+      </c>
+      <c r="C357">
+        <v>5</v>
+      </c>
+      <c r="D357" t="s">
         <v>16</v>
       </c>
-      <c r="B357" t="s">
-        <v>5</v>
-      </c>
-      <c r="C357">
-        <v>5</v>
-      </c>
-      <c r="D357" t="s">
-        <v>6</v>
-      </c>
       <c r="E357">
-        <v>25.37</v>
+        <v>25.61</v>
       </c>
       <c r="F357">
-        <v>25.54</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
+        <v>15</v>
+      </c>
+      <c r="B358" t="s">
+        <v>5</v>
+      </c>
+      <c r="C358">
+        <v>6</v>
+      </c>
+      <c r="D358" t="s">
         <v>16</v>
       </c>
-      <c r="B358" t="s">
-        <v>5</v>
-      </c>
-      <c r="C358">
-        <v>6</v>
-      </c>
-      <c r="D358" t="s">
-        <v>6</v>
-      </c>
       <c r="E358">
-        <v>26.44</v>
+        <v>25.78</v>
       </c>
       <c r="F358">
-        <v>26.25</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
+        <v>15</v>
+      </c>
+      <c r="B359" t="s">
+        <v>5</v>
+      </c>
+      <c r="C359">
+        <v>7</v>
+      </c>
+      <c r="D359" t="s">
         <v>16</v>
       </c>
-      <c r="B359" t="s">
-        <v>5</v>
-      </c>
-      <c r="C359">
-        <v>7</v>
-      </c>
-      <c r="D359" t="s">
-        <v>6</v>
-      </c>
       <c r="E359">
-        <v>25.9</v>
+        <v>25.3</v>
       </c>
       <c r="F359">
-        <v>25.92</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
+        <v>15</v>
+      </c>
+      <c r="B360" t="s">
+        <v>5</v>
+      </c>
+      <c r="C360">
+        <v>8</v>
+      </c>
+      <c r="D360" t="s">
         <v>16</v>
       </c>
-      <c r="B360" t="s">
-        <v>5</v>
-      </c>
-      <c r="C360">
-        <v>8</v>
-      </c>
-      <c r="D360" t="s">
-        <v>6</v>
-      </c>
       <c r="E360">
-        <v>26.27</v>
+        <v>24.99</v>
       </c>
       <c r="F360">
-        <v>25.35</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B361" t="s">
         <v>7</v>
@@ -7727,18 +7705,18 @@
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E361">
-        <v>26.63</v>
+        <v>26.36</v>
       </c>
       <c r="F361">
-        <v>26.2</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B362" t="s">
         <v>7</v>
@@ -7747,18 +7725,18 @@
         <v>2</v>
       </c>
       <c r="D362" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E362">
-        <v>25.52</v>
+        <v>26.97</v>
       </c>
       <c r="F362">
-        <v>26.17</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B363" t="s">
         <v>7</v>
@@ -7767,98 +7745,98 @@
         <v>3</v>
       </c>
       <c r="D363" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E363">
-        <v>27.82</v>
+        <v>26.39</v>
       </c>
       <c r="F363">
-        <v>27.5</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
+        <v>15</v>
+      </c>
+      <c r="B364" t="s">
+        <v>7</v>
+      </c>
+      <c r="C364">
+        <v>4</v>
+      </c>
+      <c r="D364" t="s">
         <v>16</v>
       </c>
-      <c r="B364" t="s">
-        <v>7</v>
-      </c>
-      <c r="C364">
-        <v>4</v>
-      </c>
-      <c r="D364" t="s">
-        <v>6</v>
-      </c>
       <c r="E364">
-        <v>27.19</v>
+        <v>25.43</v>
       </c>
       <c r="F364">
-        <v>27.7</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
+        <v>15</v>
+      </c>
+      <c r="B365" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365">
+        <v>5</v>
+      </c>
+      <c r="D365" t="s">
         <v>16</v>
       </c>
-      <c r="B365" t="s">
-        <v>7</v>
-      </c>
-      <c r="C365">
-        <v>5</v>
-      </c>
-      <c r="D365" t="s">
-        <v>6</v>
-      </c>
       <c r="E365">
-        <v>26.08</v>
+        <v>24.74</v>
       </c>
       <c r="F365">
-        <v>26.31</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
+        <v>15</v>
+      </c>
+      <c r="B366" t="s">
+        <v>7</v>
+      </c>
+      <c r="C366">
+        <v>6</v>
+      </c>
+      <c r="D366" t="s">
         <v>16</v>
       </c>
-      <c r="B366" t="s">
-        <v>7</v>
-      </c>
-      <c r="C366">
-        <v>6</v>
-      </c>
-      <c r="D366" t="s">
-        <v>6</v>
-      </c>
       <c r="E366">
-        <v>26.1</v>
+        <v>25.67</v>
       </c>
       <c r="F366">
-        <v>26.08</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
+        <v>15</v>
+      </c>
+      <c r="B367" t="s">
+        <v>7</v>
+      </c>
+      <c r="C367">
+        <v>7</v>
+      </c>
+      <c r="D367" t="s">
         <v>16</v>
       </c>
-      <c r="B367" t="s">
-        <v>7</v>
-      </c>
-      <c r="C367">
-        <v>7</v>
-      </c>
-      <c r="D367" t="s">
-        <v>6</v>
-      </c>
       <c r="E367">
-        <v>26.58</v>
+        <v>26.68</v>
       </c>
       <c r="F367">
-        <v>26.63</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B368" t="s">
         <v>8</v>
@@ -7867,18 +7845,18 @@
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E368">
-        <v>26.94</v>
+        <v>26.27</v>
       </c>
       <c r="F368">
-        <v>25.7</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B369" t="s">
         <v>8</v>
@@ -7887,18 +7865,18 @@
         <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E369">
-        <v>25.43</v>
+        <v>25.42</v>
       </c>
       <c r="F369">
-        <v>25.64</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B370" t="s">
         <v>8</v>
@@ -7907,118 +7885,118 @@
         <v>3</v>
       </c>
       <c r="D370" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E370">
-        <v>26.38</v>
+        <v>25.73</v>
       </c>
       <c r="F370">
-        <v>25.77</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
+        <v>15</v>
+      </c>
+      <c r="B371" t="s">
+        <v>8</v>
+      </c>
+      <c r="C371">
+        <v>4</v>
+      </c>
+      <c r="D371" t="s">
         <v>16</v>
       </c>
-      <c r="B371" t="s">
-        <v>8</v>
-      </c>
-      <c r="C371">
-        <v>4</v>
-      </c>
-      <c r="D371" t="s">
-        <v>6</v>
-      </c>
       <c r="E371">
-        <v>26.16</v>
+        <v>26.77</v>
       </c>
       <c r="F371">
-        <v>26.08</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
+        <v>15</v>
+      </c>
+      <c r="B372" t="s">
+        <v>8</v>
+      </c>
+      <c r="C372">
+        <v>5</v>
+      </c>
+      <c r="D372" t="s">
         <v>16</v>
       </c>
-      <c r="B372" t="s">
-        <v>8</v>
-      </c>
-      <c r="C372">
-        <v>5</v>
-      </c>
-      <c r="D372" t="s">
-        <v>6</v>
-      </c>
       <c r="E372">
-        <v>25.96</v>
+        <v>26.27</v>
       </c>
       <c r="F372">
-        <v>25.7</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
+        <v>15</v>
+      </c>
+      <c r="B373" t="s">
+        <v>8</v>
+      </c>
+      <c r="C373">
+        <v>6</v>
+      </c>
+      <c r="D373" t="s">
         <v>16</v>
       </c>
-      <c r="B373" t="s">
-        <v>8</v>
-      </c>
-      <c r="C373">
-        <v>6</v>
-      </c>
-      <c r="D373" t="s">
-        <v>6</v>
-      </c>
       <c r="E373">
-        <v>26.19</v>
+        <v>25.42</v>
       </c>
       <c r="F373">
-        <v>26.97</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
+        <v>15</v>
+      </c>
+      <c r="B374" t="s">
+        <v>8</v>
+      </c>
+      <c r="C374">
+        <v>7</v>
+      </c>
+      <c r="D374" t="s">
         <v>16</v>
       </c>
-      <c r="B374" t="s">
-        <v>8</v>
-      </c>
-      <c r="C374">
-        <v>7</v>
-      </c>
-      <c r="D374" t="s">
-        <v>6</v>
-      </c>
       <c r="E374">
-        <v>25.77</v>
+        <v>26.62</v>
       </c>
       <c r="F374">
-        <v>25.45</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
+        <v>15</v>
+      </c>
+      <c r="B375" t="s">
+        <v>8</v>
+      </c>
+      <c r="C375">
+        <v>8</v>
+      </c>
+      <c r="D375" t="s">
         <v>16</v>
       </c>
-      <c r="B375" t="s">
-        <v>8</v>
-      </c>
-      <c r="C375">
-        <v>8</v>
-      </c>
-      <c r="D375" t="s">
-        <v>6</v>
-      </c>
       <c r="E375">
+        <v>25.97</v>
+      </c>
+      <c r="F375">
         <v>25.36</v>
-      </c>
-      <c r="F375">
-        <v>25.49</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B376" t="s">
         <v>9</v>
@@ -8027,18 +8005,18 @@
         <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E376">
-        <v>22.07</v>
+        <v>25.33</v>
       </c>
       <c r="F376">
-        <v>21.92</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B377" t="s">
         <v>9</v>
@@ -8047,18 +8025,18 @@
         <v>2</v>
       </c>
       <c r="D377" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E377">
-        <v>16.13</v>
+        <v>26.14</v>
       </c>
       <c r="F377">
-        <v>16.29</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B378" t="s">
         <v>9</v>
@@ -8067,18 +8045,18 @@
         <v>3</v>
       </c>
       <c r="D378" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E378">
-        <v>14.65</v>
+        <v>27.1</v>
       </c>
       <c r="F378">
-        <v>15.03</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B379" t="s">
         <v>9</v>
@@ -8087,18 +8065,18 @@
         <v>4</v>
       </c>
       <c r="D379" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E379">
-        <v>13.11</v>
+        <v>24.66</v>
       </c>
       <c r="F379">
-        <v>15.1</v>
+        <v>24.27</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B380" t="s">
         <v>9</v>
@@ -8107,18 +8085,18 @@
         <v>5</v>
       </c>
       <c r="D380" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E380">
-        <v>15.09</v>
+        <v>26.67</v>
       </c>
       <c r="F380">
-        <v>15.19</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B381" t="s">
         <v>9</v>
@@ -8127,18 +8105,18 @@
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E381">
-        <v>15</v>
+        <v>26.17</v>
       </c>
       <c r="F381">
-        <v>14.85</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B382" t="s">
         <v>9</v>
@@ -8147,18 +8125,18 @@
         <v>7</v>
       </c>
       <c r="D382" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E382">
-        <v>16.04</v>
+        <v>26.89</v>
       </c>
       <c r="F382">
-        <v>16.16</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B383" t="s">
         <v>9</v>
@@ -8167,18 +8145,18 @@
         <v>8</v>
       </c>
       <c r="D383" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E383">
-        <v>15.38</v>
+        <v>25.67</v>
       </c>
       <c r="F383">
-        <v>15.06</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B384" t="s">
         <v>10</v>
@@ -8187,18 +8165,18 @@
         <v>1</v>
       </c>
       <c r="D384" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E384">
-        <v>15.83</v>
+        <v>25.11</v>
       </c>
       <c r="F384">
-        <v>15.99</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B385" t="s">
         <v>10</v>
@@ -8207,18 +8185,18 @@
         <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E385">
-        <v>14.15</v>
+        <v>22.3</v>
       </c>
       <c r="F385">
-        <v>14.44</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B386" t="s">
         <v>10</v>
@@ -8227,18 +8205,18 @@
         <v>3</v>
       </c>
       <c r="D386" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E386">
-        <v>13.71</v>
+        <v>24.02</v>
       </c>
       <c r="F386">
-        <v>13.74</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B387" t="s">
         <v>10</v>
@@ -8247,18 +8225,18 @@
         <v>4</v>
       </c>
       <c r="D387" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E387">
-        <v>15.34</v>
+        <v>24.83</v>
       </c>
       <c r="F387">
-        <v>15.22</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B388" t="s">
         <v>10</v>
@@ -8267,18 +8245,18 @@
         <v>5</v>
       </c>
       <c r="D388" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E388">
-        <v>15.69</v>
+        <v>25.38</v>
       </c>
       <c r="F388">
-        <v>15.72</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B389" t="s">
         <v>10</v>
@@ -8287,18 +8265,18 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E389">
-        <v>16.100000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="F389">
-        <v>16.329999999999998</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B390" t="s">
         <v>10</v>
@@ -8307,18 +8285,18 @@
         <v>7</v>
       </c>
       <c r="D390" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E390">
-        <v>14.93</v>
+        <v>26.11</v>
       </c>
       <c r="F390">
-        <v>14.6</v>
+        <v>26.62</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B391" t="s">
         <v>10</v>
@@ -8327,18 +8305,18 @@
         <v>8</v>
       </c>
       <c r="D391" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E391">
-        <v>15.51</v>
+        <v>23.72</v>
       </c>
       <c r="F391">
-        <v>15.73</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B392" t="s">
         <v>5</v>
@@ -8347,18 +8325,18 @@
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E392">
-        <v>20.07</v>
+        <v>28.72</v>
       </c>
       <c r="F392">
-        <v>20.71</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B393" t="s">
         <v>5</v>
@@ -8367,18 +8345,18 @@
         <v>2</v>
       </c>
       <c r="D393" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E393">
-        <v>20.27</v>
+        <v>27.1</v>
       </c>
       <c r="F393">
-        <v>20.420000000000002</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B394" t="s">
         <v>5</v>
@@ -8387,118 +8365,118 @@
         <v>3</v>
       </c>
       <c r="D394" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E394">
-        <v>19.22</v>
+        <v>26.29</v>
       </c>
       <c r="F394">
-        <v>19</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
+        <v>15</v>
+      </c>
+      <c r="B395" t="s">
+        <v>5</v>
+      </c>
+      <c r="C395">
+        <v>4</v>
+      </c>
+      <c r="D395" t="s">
         <v>17</v>
       </c>
-      <c r="B395" t="s">
-        <v>5</v>
-      </c>
-      <c r="C395">
-        <v>4</v>
-      </c>
-      <c r="D395" t="s">
-        <v>6</v>
-      </c>
       <c r="E395">
-        <v>18.86</v>
+        <v>25.61</v>
       </c>
       <c r="F395">
-        <v>19.260000000000002</v>
+        <v>25.39</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
+        <v>15</v>
+      </c>
+      <c r="B396" t="s">
+        <v>5</v>
+      </c>
+      <c r="C396">
+        <v>5</v>
+      </c>
+      <c r="D396" t="s">
         <v>17</v>
       </c>
-      <c r="B396" t="s">
-        <v>5</v>
-      </c>
-      <c r="C396">
-        <v>5</v>
-      </c>
-      <c r="D396" t="s">
-        <v>6</v>
-      </c>
       <c r="E396">
-        <v>19.25</v>
+        <v>25.55</v>
       </c>
       <c r="F396">
-        <v>19.059999999999999</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
+        <v>15</v>
+      </c>
+      <c r="B397" t="s">
+        <v>5</v>
+      </c>
+      <c r="C397">
+        <v>6</v>
+      </c>
+      <c r="D397" t="s">
         <v>17</v>
       </c>
-      <c r="B397" t="s">
-        <v>5</v>
-      </c>
-      <c r="C397">
-        <v>6</v>
-      </c>
-      <c r="D397" t="s">
-        <v>6</v>
-      </c>
       <c r="E397">
-        <v>19.29</v>
+        <v>25.51</v>
       </c>
       <c r="F397">
-        <v>19.18</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
+        <v>15</v>
+      </c>
+      <c r="B398" t="s">
+        <v>5</v>
+      </c>
+      <c r="C398">
+        <v>7</v>
+      </c>
+      <c r="D398" t="s">
         <v>17</v>
       </c>
-      <c r="B398" t="s">
-        <v>5</v>
-      </c>
-      <c r="C398">
-        <v>7</v>
-      </c>
-      <c r="D398" t="s">
-        <v>6</v>
-      </c>
       <c r="E398">
-        <v>18.350000000000001</v>
+        <v>23.95</v>
       </c>
       <c r="F398">
-        <v>18.12</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
+        <v>15</v>
+      </c>
+      <c r="B399" t="s">
+        <v>5</v>
+      </c>
+      <c r="C399">
+        <v>8</v>
+      </c>
+      <c r="D399" t="s">
         <v>17</v>
       </c>
-      <c r="B399" t="s">
-        <v>5</v>
-      </c>
-      <c r="C399">
-        <v>8</v>
-      </c>
-      <c r="D399" t="s">
-        <v>6</v>
-      </c>
       <c r="E399">
-        <v>18.29</v>
+        <v>25.39</v>
       </c>
       <c r="F399">
-        <v>18.39</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B400" t="s">
         <v>7</v>
@@ -8507,18 +8485,18 @@
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E400">
-        <v>19.75</v>
+        <v>27.94</v>
       </c>
       <c r="F400">
-        <v>19.940000000000001</v>
+        <v>27.98</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B401" t="s">
         <v>7</v>
@@ -8527,18 +8505,18 @@
         <v>2</v>
       </c>
       <c r="D401" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E401">
-        <v>20.8</v>
+        <v>27.65</v>
       </c>
       <c r="F401">
-        <v>20.12</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B402" t="s">
         <v>7</v>
@@ -8547,98 +8525,98 @@
         <v>3</v>
       </c>
       <c r="D402" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E402">
-        <v>19.77</v>
+        <v>27.52</v>
       </c>
       <c r="F402">
-        <v>20.03</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
+        <v>15</v>
+      </c>
+      <c r="B403" t="s">
+        <v>7</v>
+      </c>
+      <c r="C403">
+        <v>4</v>
+      </c>
+      <c r="D403" t="s">
         <v>17</v>
       </c>
-      <c r="B403" t="s">
-        <v>7</v>
-      </c>
-      <c r="C403">
-        <v>4</v>
-      </c>
-      <c r="D403" t="s">
-        <v>6</v>
-      </c>
       <c r="E403">
-        <v>19.670000000000002</v>
+        <v>26.17</v>
       </c>
       <c r="F403">
-        <v>19.760000000000002</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
+        <v>15</v>
+      </c>
+      <c r="B404" t="s">
+        <v>7</v>
+      </c>
+      <c r="C404">
+        <v>5</v>
+      </c>
+      <c r="D404" t="s">
         <v>17</v>
       </c>
-      <c r="B404" t="s">
-        <v>7</v>
-      </c>
-      <c r="C404">
-        <v>5</v>
-      </c>
-      <c r="D404" t="s">
-        <v>6</v>
-      </c>
       <c r="E404">
-        <v>19.739999999999998</v>
+        <v>26.87</v>
       </c>
       <c r="F404">
-        <v>19.54</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
+        <v>15</v>
+      </c>
+      <c r="B405" t="s">
+        <v>7</v>
+      </c>
+      <c r="C405">
+        <v>6</v>
+      </c>
+      <c r="D405" t="s">
         <v>17</v>
       </c>
-      <c r="B405" t="s">
-        <v>7</v>
-      </c>
-      <c r="C405">
-        <v>6</v>
-      </c>
-      <c r="D405" t="s">
-        <v>6</v>
-      </c>
       <c r="E405">
-        <v>21.21</v>
+        <v>27.6</v>
       </c>
       <c r="F405">
-        <v>21.6</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
+        <v>15</v>
+      </c>
+      <c r="B406" t="s">
+        <v>7</v>
+      </c>
+      <c r="C406">
+        <v>7</v>
+      </c>
+      <c r="D406" t="s">
         <v>17</v>
       </c>
-      <c r="B406" t="s">
-        <v>7</v>
-      </c>
-      <c r="C406">
-        <v>7</v>
-      </c>
-      <c r="D406" t="s">
-        <v>6</v>
-      </c>
       <c r="E406">
-        <v>20.170000000000002</v>
+        <v>27.4</v>
       </c>
       <c r="F406">
-        <v>20.45</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B407" t="s">
         <v>8</v>
@@ -8647,18 +8625,18 @@
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E407">
-        <v>21</v>
+        <v>26.83</v>
       </c>
       <c r="F407">
-        <v>20.89</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B408" t="s">
         <v>8</v>
@@ -8667,18 +8645,18 @@
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E408">
-        <v>20.43</v>
+        <v>26.22</v>
       </c>
       <c r="F408">
-        <v>20.25</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B409" t="s">
         <v>8</v>
@@ -8687,118 +8665,118 @@
         <v>3</v>
       </c>
       <c r="D409" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E409">
-        <v>20.25</v>
+        <v>26.26</v>
       </c>
       <c r="F409">
-        <v>19.55</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
+        <v>15</v>
+      </c>
+      <c r="B410" t="s">
+        <v>8</v>
+      </c>
+      <c r="C410">
+        <v>4</v>
+      </c>
+      <c r="D410" t="s">
         <v>17</v>
       </c>
-      <c r="B410" t="s">
-        <v>8</v>
-      </c>
-      <c r="C410">
-        <v>4</v>
-      </c>
-      <c r="D410" t="s">
-        <v>6</v>
-      </c>
       <c r="E410">
-        <v>21.82</v>
+        <v>28.03</v>
       </c>
       <c r="F410">
-        <v>22.25</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
+        <v>15</v>
+      </c>
+      <c r="B411" t="s">
+        <v>8</v>
+      </c>
+      <c r="C411">
+        <v>5</v>
+      </c>
+      <c r="D411" t="s">
         <v>17</v>
       </c>
-      <c r="B411" t="s">
-        <v>8</v>
-      </c>
-      <c r="C411">
-        <v>5</v>
-      </c>
-      <c r="D411" t="s">
-        <v>6</v>
-      </c>
       <c r="E411">
-        <v>20.14</v>
+        <v>27.3</v>
       </c>
       <c r="F411">
-        <v>20.37</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
+        <v>15</v>
+      </c>
+      <c r="B412" t="s">
+        <v>8</v>
+      </c>
+      <c r="C412">
+        <v>6</v>
+      </c>
+      <c r="D412" t="s">
         <v>17</v>
       </c>
-      <c r="B412" t="s">
-        <v>8</v>
-      </c>
-      <c r="C412">
-        <v>6</v>
-      </c>
-      <c r="D412" t="s">
-        <v>6</v>
-      </c>
       <c r="E412">
-        <v>21.4</v>
+        <v>27.78</v>
       </c>
       <c r="F412">
-        <v>21.1</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
+        <v>15</v>
+      </c>
+      <c r="B413" t="s">
+        <v>8</v>
+      </c>
+      <c r="C413">
+        <v>7</v>
+      </c>
+      <c r="D413" t="s">
         <v>17</v>
       </c>
-      <c r="B413" t="s">
-        <v>8</v>
-      </c>
-      <c r="C413">
-        <v>7</v>
-      </c>
-      <c r="D413" t="s">
-        <v>6</v>
-      </c>
       <c r="E413">
-        <v>20.48</v>
+        <v>28.54</v>
       </c>
       <c r="F413">
-        <v>20.88</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
+        <v>15</v>
+      </c>
+      <c r="B414" t="s">
+        <v>8</v>
+      </c>
+      <c r="C414">
+        <v>8</v>
+      </c>
+      <c r="D414" t="s">
         <v>17</v>
       </c>
-      <c r="B414" t="s">
-        <v>8</v>
-      </c>
-      <c r="C414">
-        <v>8</v>
-      </c>
-      <c r="D414" t="s">
-        <v>6</v>
-      </c>
       <c r="E414">
-        <v>19.260000000000002</v>
+        <v>26.27</v>
       </c>
       <c r="F414">
-        <v>19.850000000000001</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B415" t="s">
         <v>9</v>
@@ -8807,18 +8785,18 @@
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E415">
-        <v>20.64</v>
+        <v>26.73</v>
       </c>
       <c r="F415">
-        <v>20.07</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B416" t="s">
         <v>9</v>
@@ -8827,18 +8805,18 @@
         <v>2</v>
       </c>
       <c r="D416" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E416">
-        <v>20.149999999999999</v>
+        <v>26.04</v>
       </c>
       <c r="F416">
-        <v>19.52</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B417" t="s">
         <v>9</v>
@@ -8847,18 +8825,18 @@
         <v>3</v>
       </c>
       <c r="D417" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E417">
-        <v>20.420000000000002</v>
+        <v>28.41</v>
       </c>
       <c r="F417">
-        <v>20.71</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B418" t="s">
         <v>9</v>
@@ -8867,18 +8845,18 @@
         <v>4</v>
       </c>
       <c r="D418" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E418">
-        <v>19.89</v>
+        <v>25</v>
       </c>
       <c r="F418">
-        <v>19.23</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B419" t="s">
         <v>9</v>
@@ -8887,18 +8865,18 @@
         <v>5</v>
       </c>
       <c r="D419" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E419">
-        <v>20.81</v>
+        <v>27.06</v>
       </c>
       <c r="F419">
-        <v>20.190000000000001</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B420" t="s">
         <v>9</v>
@@ -8907,18 +8885,18 @@
         <v>6</v>
       </c>
       <c r="D420" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E420">
-        <v>20.21</v>
+        <v>26.7</v>
       </c>
       <c r="F420">
-        <v>20.260000000000002</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B421" t="s">
         <v>9</v>
@@ -8927,18 +8905,18 @@
         <v>7</v>
       </c>
       <c r="D421" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E421">
-        <v>20.21</v>
+        <v>26.54</v>
       </c>
       <c r="F421">
-        <v>20.43</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B422" t="s">
         <v>9</v>
@@ -8947,18 +8925,18 @@
         <v>8</v>
       </c>
       <c r="D422" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E422">
-        <v>20.79</v>
+        <v>26.44</v>
       </c>
       <c r="F422">
-        <v>20.69</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B423" t="s">
         <v>10</v>
@@ -8967,18 +8945,18 @@
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E423">
-        <v>19.309999999999999</v>
+        <v>25.48</v>
       </c>
       <c r="F423">
-        <v>19.510000000000002</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B424" t="s">
         <v>10</v>
@@ -8987,18 +8965,18 @@
         <v>2</v>
       </c>
       <c r="D424" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E424">
-        <v>19.399999999999999</v>
+        <v>24.51</v>
       </c>
       <c r="F424">
-        <v>19.239999999999998</v>
+        <v>24.74</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B425" t="s">
         <v>10</v>
@@ -9007,18 +8985,18 @@
         <v>3</v>
       </c>
       <c r="D425" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E425">
-        <v>20.66</v>
+        <v>25.74</v>
       </c>
       <c r="F425">
-        <v>20.190000000000001</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B426" t="s">
         <v>10</v>
@@ -9027,18 +9005,18 @@
         <v>4</v>
       </c>
       <c r="D426" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E426">
-        <v>20.2</v>
+        <v>25.8</v>
       </c>
       <c r="F426">
-        <v>19.66</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B427" t="s">
         <v>10</v>
@@ -9047,18 +9025,18 @@
         <v>5</v>
       </c>
       <c r="D427" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E427">
-        <v>20.22</v>
+        <v>26.13</v>
       </c>
       <c r="F427">
-        <v>21.17</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B428" t="s">
         <v>10</v>
@@ -9067,18 +9045,18 @@
         <v>6</v>
       </c>
       <c r="D428" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E428">
-        <v>21.97</v>
+        <v>27.78</v>
       </c>
       <c r="F428">
-        <v>21.83</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B429" t="s">
         <v>10</v>
@@ -9087,18 +9065,18 @@
         <v>7</v>
       </c>
       <c r="D429" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E429">
-        <v>20.23</v>
+        <v>29.2</v>
       </c>
       <c r="F429">
-        <v>20.440000000000001</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B430" t="s">
         <v>10</v>
@@ -9107,18 +9085,18 @@
         <v>8</v>
       </c>
       <c r="D430" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E430">
-        <v>20.67</v>
+        <v>25.92</v>
       </c>
       <c r="F430">
-        <v>20.46</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B431" t="s">
         <v>5</v>
@@ -9127,18 +9105,18 @@
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E431">
-        <v>23</v>
+        <v>32.090000000000003</v>
       </c>
       <c r="F431">
-        <v>22.85</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B432" t="s">
         <v>5</v>
@@ -9147,18 +9125,18 @@
         <v>2</v>
       </c>
       <c r="D432" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E432">
-        <v>23.25</v>
+        <v>30.83</v>
       </c>
       <c r="F432">
-        <v>23.24</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B433" t="s">
         <v>5</v>
@@ -9167,18 +9145,18 @@
         <v>3</v>
       </c>
       <c r="D433" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E433">
-        <v>23.1</v>
+        <v>31.23</v>
       </c>
       <c r="F433">
-        <v>24.06</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B434" t="s">
         <v>5</v>
@@ -9187,18 +9165,18 @@
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E434">
-        <v>24.07</v>
+        <v>30.27</v>
       </c>
       <c r="F434">
-        <v>23.52</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B435" t="s">
         <v>5</v>
@@ -9207,18 +9185,18 @@
         <v>5</v>
       </c>
       <c r="D435" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E435">
-        <v>23.92</v>
+        <v>30.46</v>
       </c>
       <c r="F435">
-        <v>23.91</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B436" t="s">
         <v>5</v>
@@ -9227,18 +9205,18 @@
         <v>6</v>
       </c>
       <c r="D436" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E436">
-        <v>23.56</v>
+        <v>30.15</v>
       </c>
       <c r="F436">
-        <v>23.46</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B437" t="s">
         <v>5</v>
@@ -9247,18 +9225,18 @@
         <v>7</v>
       </c>
       <c r="D437" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E437">
-        <v>23.23</v>
+        <v>29.92</v>
       </c>
       <c r="F437">
-        <v>23.27</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B438" t="s">
         <v>5</v>
@@ -9267,18 +9245,18 @@
         <v>8</v>
       </c>
       <c r="D438" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E438">
-        <v>24.74</v>
+        <v>30.18</v>
       </c>
       <c r="F438">
-        <v>25.8</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B439" t="s">
         <v>7</v>
@@ -9287,18 +9265,18 @@
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E439">
-        <v>24.47</v>
+        <v>31.09</v>
       </c>
       <c r="F439">
-        <v>23.95</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B440" t="s">
         <v>7</v>
@@ -9307,18 +9285,18 @@
         <v>2</v>
       </c>
       <c r="D440" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E440">
-        <v>23.16</v>
+        <v>31.06</v>
       </c>
       <c r="F440">
-        <v>22.82</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B441" t="s">
         <v>7</v>
@@ -9327,18 +9305,18 @@
         <v>3</v>
       </c>
       <c r="D441" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E441">
-        <v>24.18</v>
+        <v>31.32</v>
       </c>
       <c r="F441">
-        <v>23.62</v>
+        <v>31.37</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B442" t="s">
         <v>7</v>
@@ -9347,18 +9325,18 @@
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E442">
-        <v>25.22</v>
+        <v>31.79</v>
       </c>
       <c r="F442">
-        <v>25.53</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B443" t="s">
         <v>7</v>
@@ -9367,18 +9345,18 @@
         <v>5</v>
       </c>
       <c r="D443" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E443">
-        <v>24.34</v>
+        <v>31.15</v>
       </c>
       <c r="F443">
-        <v>24.66</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B444" t="s">
         <v>7</v>
@@ -9387,18 +9365,18 @@
         <v>6</v>
       </c>
       <c r="D444" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E444">
-        <v>22.21</v>
+        <v>31.08</v>
       </c>
       <c r="F444">
-        <v>22.1</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B445" t="s">
         <v>7</v>
@@ -9407,18 +9385,18 @@
         <v>7</v>
       </c>
       <c r="D445" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E445">
-        <v>23.31</v>
+        <v>31.5</v>
       </c>
       <c r="F445">
-        <v>24.28</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B446" t="s">
         <v>8</v>
@@ -9427,18 +9405,18 @@
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E446">
-        <v>22.8</v>
+        <v>31.4</v>
       </c>
       <c r="F446">
-        <v>22.24</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B447" t="s">
         <v>8</v>
@@ -9447,18 +9425,18 @@
         <v>2</v>
       </c>
       <c r="D447" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E447">
-        <v>22.47</v>
+        <v>30.55</v>
       </c>
       <c r="F447">
-        <v>23.27</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B448" t="s">
         <v>8</v>
@@ -9467,18 +9445,18 @@
         <v>3</v>
       </c>
       <c r="D448" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E448">
-        <v>23.09</v>
+        <v>31.94</v>
       </c>
       <c r="F448">
-        <v>23.13</v>
+        <v>32.020000000000003</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B449" t="s">
         <v>8</v>
@@ -9487,18 +9465,18 @@
         <v>4</v>
       </c>
       <c r="D449" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E449">
-        <v>23.53</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="F449">
-        <v>23.43</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B450" t="s">
         <v>8</v>
@@ -9507,18 +9485,18 @@
         <v>5</v>
       </c>
       <c r="D450" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E450">
-        <v>24.16</v>
+        <v>32.1</v>
       </c>
       <c r="F450">
-        <v>24.07</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B451" t="s">
         <v>8</v>
@@ -9527,18 +9505,18 @@
         <v>6</v>
       </c>
       <c r="D451" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E451">
-        <v>23.09</v>
+        <v>32.369999999999997</v>
       </c>
       <c r="F451">
-        <v>22.85</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B452" t="s">
         <v>8</v>
@@ -9547,18 +9525,18 @@
         <v>7</v>
       </c>
       <c r="D452" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E452">
-        <v>22.12</v>
+        <v>32.85</v>
       </c>
       <c r="F452">
-        <v>23.01</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B453" t="s">
         <v>8</v>
@@ -9567,18 +9545,18 @@
         <v>8</v>
       </c>
       <c r="D453" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E453">
-        <v>25.27</v>
+        <v>30.39</v>
       </c>
       <c r="F453">
-        <v>24.41</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B454" t="s">
         <v>9</v>
@@ -9587,18 +9565,18 @@
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E454">
-        <v>25.27</v>
+        <v>32.33</v>
       </c>
       <c r="F454">
-        <v>24.41</v>
+        <v>32.28</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B455" t="s">
         <v>9</v>
@@ -9607,18 +9585,18 @@
         <v>2</v>
       </c>
       <c r="D455" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E455">
-        <v>26.27</v>
+        <v>31.49</v>
       </c>
       <c r="F455">
-        <v>26.42</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B456" t="s">
         <v>9</v>
@@ -9627,18 +9605,18 @@
         <v>3</v>
       </c>
       <c r="D456" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E456">
-        <v>22.72</v>
+        <v>32.5</v>
       </c>
       <c r="F456">
-        <v>22.25</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B457" t="s">
         <v>9</v>
@@ -9647,18 +9625,18 @@
         <v>4</v>
       </c>
       <c r="D457" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E457">
-        <v>22.52</v>
+        <v>28.24</v>
       </c>
       <c r="F457">
-        <v>22.98</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B458" t="s">
         <v>9</v>
@@ -9667,18 +9645,18 @@
         <v>5</v>
       </c>
       <c r="D458" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E458">
-        <v>21.78</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="F458">
-        <v>21.19</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B459" t="s">
         <v>9</v>
@@ -9687,18 +9665,18 @@
         <v>6</v>
       </c>
       <c r="D459" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E459">
-        <v>22.32</v>
+        <v>30.59</v>
       </c>
       <c r="F459">
-        <v>23.09</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B460" t="s">
         <v>9</v>
@@ -9707,18 +9685,18 @@
         <v>7</v>
       </c>
       <c r="D460" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E460">
-        <v>23.33</v>
+        <v>31.47</v>
       </c>
       <c r="F460">
-        <v>22.69</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -9727,18 +9705,18 @@
         <v>8</v>
       </c>
       <c r="D461" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E461">
-        <v>22.85</v>
+        <v>30.28</v>
       </c>
       <c r="F461">
-        <v>23.16</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B462" t="s">
         <v>10</v>
@@ -9747,18 +9725,18 @@
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E462">
-        <v>21.16</v>
+        <v>32.11</v>
       </c>
       <c r="F462">
-        <v>21.58</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B463" t="s">
         <v>10</v>
@@ -9767,18 +9745,18 @@
         <v>2</v>
       </c>
       <c r="D463" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E463">
-        <v>21.05</v>
+        <v>30.01</v>
       </c>
       <c r="F463">
-        <v>21.62</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B464" t="s">
         <v>10</v>
@@ -9787,18 +9765,18 @@
         <v>3</v>
       </c>
       <c r="D464" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E464">
-        <v>22.3</v>
+        <v>30.26</v>
       </c>
       <c r="F464">
-        <v>22.52</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B465" t="s">
         <v>10</v>
@@ -9807,18 +9785,18 @@
         <v>4</v>
       </c>
       <c r="D465" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E465">
-        <v>20.86</v>
+        <v>29.83</v>
       </c>
       <c r="F465">
-        <v>20.99</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B466" t="s">
         <v>10</v>
@@ -9827,18 +9805,18 @@
         <v>5</v>
       </c>
       <c r="D466" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E466">
-        <v>19.8</v>
+        <v>30.06</v>
       </c>
       <c r="F466">
-        <v>20.58</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B467" t="s">
         <v>10</v>
@@ -9847,18 +9825,18 @@
         <v>6</v>
       </c>
       <c r="D467" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E467">
-        <v>20.97</v>
+        <v>31.04</v>
       </c>
       <c r="F467">
-        <v>20.09</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B468" t="s">
         <v>10</v>
@@ -9867,18 +9845,18 @@
         <v>7</v>
       </c>
       <c r="D468" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E468">
-        <v>21.3</v>
+        <v>32.07</v>
       </c>
       <c r="F468">
-        <v>20.99</v>
+        <v>32.020000000000003</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B469" t="s">
         <v>10</v>
@@ -9887,18 +9865,18 @@
         <v>8</v>
       </c>
       <c r="D469" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E469">
-        <v>20.73</v>
+        <v>30.31</v>
       </c>
       <c r="F469">
-        <v>19.79</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B470" t="s">
         <v>5</v>
@@ -9907,18 +9885,18 @@
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E470">
-        <v>26.11</v>
+        <v>31</v>
       </c>
       <c r="F470">
-        <v>26.49</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B471" t="s">
         <v>5</v>
@@ -9927,18 +9905,18 @@
         <v>2</v>
       </c>
       <c r="D471" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E471">
-        <v>24.76</v>
+        <v>30.22</v>
       </c>
       <c r="F471">
-        <v>24.42</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B472" t="s">
         <v>5</v>
@@ -9947,18 +9925,18 @@
         <v>3</v>
       </c>
       <c r="D472" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E472">
-        <v>29.15</v>
+        <v>29.6</v>
       </c>
       <c r="F472">
-        <v>29.06</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B473" t="s">
         <v>5</v>
@@ -9967,18 +9945,18 @@
         <v>4</v>
       </c>
       <c r="D473" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E473">
-        <v>26.09</v>
+        <v>29.99</v>
       </c>
       <c r="F473">
-        <v>26.88</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B474" t="s">
         <v>5</v>
@@ -9987,18 +9965,18 @@
         <v>5</v>
       </c>
       <c r="D474" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E474">
-        <v>26.6</v>
+        <v>29.4</v>
       </c>
       <c r="F474">
-        <v>26.67</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B475" t="s">
         <v>5</v>
@@ -10007,18 +9985,18 @@
         <v>6</v>
       </c>
       <c r="D475" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E475">
-        <v>27.56</v>
+        <v>28.92</v>
       </c>
       <c r="F475">
-        <v>28.31</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B476" t="s">
         <v>5</v>
@@ -10027,18 +10005,18 @@
         <v>7</v>
       </c>
       <c r="D476" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E476">
-        <v>28.01</v>
+        <v>29.02</v>
       </c>
       <c r="F476">
-        <v>27.98</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B477" t="s">
         <v>5</v>
@@ -10047,18 +10025,18 @@
         <v>8</v>
       </c>
       <c r="D477" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E477">
-        <v>29.21</v>
+        <v>26.89</v>
       </c>
       <c r="F477">
-        <v>29.48</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B478" t="s">
         <v>7</v>
@@ -10067,18 +10045,18 @@
         <v>1</v>
       </c>
       <c r="D478" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E478">
-        <v>27.02</v>
+        <v>29.17</v>
       </c>
       <c r="F478">
-        <v>26.64</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B479" t="s">
         <v>7</v>
@@ -10087,18 +10065,18 @@
         <v>2</v>
       </c>
       <c r="D479" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E479">
-        <v>29.21</v>
+        <v>30.1</v>
       </c>
       <c r="F479">
-        <v>28.82</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B480" t="s">
         <v>7</v>
@@ -10107,18 +10085,18 @@
         <v>3</v>
       </c>
       <c r="D480" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E480">
-        <v>29.61</v>
+        <v>30.41</v>
       </c>
       <c r="F480">
-        <v>29.93</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B481" t="s">
         <v>7</v>
@@ -10127,18 +10105,18 @@
         <v>4</v>
       </c>
       <c r="D481" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E481">
-        <v>27.33</v>
+        <v>30.14</v>
       </c>
       <c r="F481">
-        <v>27.95</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B482" t="s">
         <v>7</v>
@@ -10147,18 +10125,18 @@
         <v>5</v>
       </c>
       <c r="D482" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E482">
-        <v>28.01</v>
+        <v>30.13</v>
       </c>
       <c r="F482">
-        <v>29.55</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B483" t="s">
         <v>7</v>
@@ -10167,18 +10145,18 @@
         <v>6</v>
       </c>
       <c r="D483" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E483">
-        <v>30.19</v>
+        <v>30.15</v>
       </c>
       <c r="F483">
-        <v>30.17</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B484" t="s">
         <v>7</v>
@@ -10187,18 +10165,18 @@
         <v>7</v>
       </c>
       <c r="D484" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E484">
-        <v>25.41</v>
+        <v>29.56</v>
       </c>
       <c r="F484">
-        <v>25.06</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B485" t="s">
         <v>8</v>
@@ -10207,18 +10185,18 @@
         <v>1</v>
       </c>
       <c r="D485" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E485">
-        <v>24.82</v>
+        <v>29.83</v>
       </c>
       <c r="F485">
-        <v>25.07</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B486" t="s">
         <v>8</v>
@@ -10227,18 +10205,18 @@
         <v>2</v>
       </c>
       <c r="D486" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E486">
-        <v>27.07</v>
+        <v>29.84</v>
       </c>
       <c r="F486">
-        <v>28.03</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B487" t="s">
         <v>8</v>
@@ -10247,18 +10225,18 @@
         <v>3</v>
       </c>
       <c r="D487" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E487">
-        <v>25.29</v>
+        <v>30.07</v>
       </c>
       <c r="F487">
-        <v>25.14</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B488" t="s">
         <v>8</v>
@@ -10267,18 +10245,18 @@
         <v>4</v>
       </c>
       <c r="D488" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E488">
-        <v>28.62</v>
+        <v>31.68</v>
       </c>
       <c r="F488">
-        <v>28.28</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B489" t="s">
         <v>8</v>
@@ -10287,18 +10265,18 @@
         <v>5</v>
       </c>
       <c r="D489" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E489">
-        <v>28.99</v>
+        <v>32.159999999999997</v>
       </c>
       <c r="F489">
-        <v>28.53</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B490" t="s">
         <v>8</v>
@@ -10307,18 +10285,18 @@
         <v>6</v>
       </c>
       <c r="D490" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E490">
-        <v>26.42</v>
+        <v>30.18</v>
       </c>
       <c r="F490">
-        <v>25.83</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B491" t="s">
         <v>8</v>
@@ -10327,18 +10305,18 @@
         <v>7</v>
       </c>
       <c r="D491" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E491">
-        <v>27.08</v>
+        <v>29.25</v>
       </c>
       <c r="F491">
-        <v>26.36</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B492" t="s">
         <v>8</v>
@@ -10347,18 +10325,18 @@
         <v>8</v>
       </c>
       <c r="D492" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E492">
-        <v>25.33</v>
+        <v>29.43</v>
       </c>
       <c r="F492">
-        <v>25.46</v>
+        <v>30.13</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B493" t="s">
         <v>9</v>
@@ -10367,18 +10345,18 @@
         <v>1</v>
       </c>
       <c r="D493" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E493">
-        <v>27.47</v>
+        <v>26.16</v>
       </c>
       <c r="F493">
-        <v>27.44</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B494" t="s">
         <v>9</v>
@@ -10387,18 +10365,18 @@
         <v>2</v>
       </c>
       <c r="D494" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E494">
-        <v>26.24</v>
+        <v>23.5</v>
       </c>
       <c r="F494">
-        <v>26.16</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B495" t="s">
         <v>9</v>
@@ -10407,18 +10385,18 @@
         <v>3</v>
       </c>
       <c r="D495" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E495">
-        <v>21.49</v>
+        <v>31.05</v>
       </c>
       <c r="F495">
-        <v>21.56</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B496" t="s">
         <v>9</v>
@@ -10427,18 +10405,18 @@
         <v>4</v>
       </c>
       <c r="D496" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E496">
-        <v>25.17</v>
+        <v>22.49</v>
       </c>
       <c r="F496">
-        <v>25.25</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B497" t="s">
         <v>9</v>
@@ -10447,18 +10425,18 @@
         <v>5</v>
       </c>
       <c r="D497" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E497">
-        <v>23.46</v>
+        <v>29.3</v>
       </c>
       <c r="F497">
-        <v>23.64</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B498" t="s">
         <v>9</v>
@@ -10467,18 +10445,18 @@
         <v>6</v>
       </c>
       <c r="D498" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E498">
-        <v>24.11</v>
+        <v>22.71</v>
       </c>
       <c r="F498">
-        <v>24.24</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B499" t="s">
         <v>9</v>
@@ -10487,18 +10465,18 @@
         <v>7</v>
       </c>
       <c r="D499" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E499">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F499">
-        <v>28.37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B500" t="s">
         <v>9</v>
@@ -10507,18 +10485,18 @@
         <v>8</v>
       </c>
       <c r="D500" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E500">
-        <v>23.94</v>
+        <v>29.74</v>
       </c>
       <c r="F500">
-        <v>24.17</v>
+        <v>29.65</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B501" t="s">
         <v>10</v>
@@ -10527,18 +10505,18 @@
         <v>1</v>
       </c>
       <c r="D501" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E501">
-        <v>23.21</v>
+        <v>19.579999999999998</v>
       </c>
       <c r="F501">
-        <v>23.9</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B502" t="s">
         <v>10</v>
@@ -10547,18 +10525,18 @@
         <v>2</v>
       </c>
       <c r="D502" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E502">
-        <v>25.34</v>
+        <v>23.66</v>
       </c>
       <c r="F502">
-        <v>25.28</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B503" t="s">
         <v>10</v>
@@ -10567,18 +10545,18 @@
         <v>3</v>
       </c>
       <c r="D503" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E503">
-        <v>23</v>
+        <v>26.99</v>
       </c>
       <c r="F503">
-        <v>23.17</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B504" t="s">
         <v>10</v>
@@ -10587,18 +10565,18 @@
         <v>4</v>
       </c>
       <c r="D504" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E504">
-        <v>30.9</v>
+        <v>22.04</v>
       </c>
       <c r="F504">
-        <v>30.1</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B505" t="s">
         <v>10</v>
@@ -10607,18 +10585,18 @@
         <v>5</v>
       </c>
       <c r="D505" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E505">
-        <v>21.92</v>
+        <v>21.61</v>
       </c>
       <c r="F505">
-        <v>22.01</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B506" t="s">
         <v>10</v>
@@ -10627,18 +10605,18 @@
         <v>6</v>
       </c>
       <c r="D506" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E506">
-        <v>24.4</v>
+        <v>21.47</v>
       </c>
       <c r="F506">
-        <v>24.46</v>
+        <v>21.17</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B507" t="s">
         <v>10</v>
@@ -10647,18 +10625,18 @@
         <v>7</v>
       </c>
       <c r="D507" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E507">
-        <v>24.29</v>
+        <v>28.55</v>
       </c>
       <c r="F507">
-        <v>24.14</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B508" t="s">
         <v>10</v>
@@ -10667,3133 +10645,13 @@
         <v>8</v>
       </c>
       <c r="D508" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E508">
-        <v>25.59</v>
+        <v>21.24</v>
       </c>
       <c r="F508">
-        <v>25.88</v>
-      </c>
-    </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A509" t="s">
-        <v>16</v>
-      </c>
-      <c r="B509" t="s">
-        <v>5</v>
-      </c>
-      <c r="C509">
-        <v>1</v>
-      </c>
-      <c r="D509" t="s">
-        <v>20</v>
-      </c>
-      <c r="E509">
-        <v>17.38</v>
-      </c>
-      <c r="F509">
-        <v>17.53</v>
-      </c>
-    </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A510" t="s">
-        <v>16</v>
-      </c>
-      <c r="B510" t="s">
-        <v>5</v>
-      </c>
-      <c r="C510">
-        <v>2</v>
-      </c>
-      <c r="D510" t="s">
-        <v>20</v>
-      </c>
-      <c r="E510">
-        <v>18</v>
-      </c>
-      <c r="F510">
-        <v>18.16</v>
-      </c>
-    </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A511" t="s">
-        <v>16</v>
-      </c>
-      <c r="B511" t="s">
-        <v>5</v>
-      </c>
-      <c r="C511">
-        <v>3</v>
-      </c>
-      <c r="D511" t="s">
-        <v>20</v>
-      </c>
-      <c r="E511">
-        <v>18.36</v>
-      </c>
-      <c r="F511">
-        <v>19.02</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A512" t="s">
-        <v>16</v>
-      </c>
-      <c r="B512" t="s">
-        <v>5</v>
-      </c>
-      <c r="C512">
-        <v>4</v>
-      </c>
-      <c r="D512" t="s">
-        <v>20</v>
-      </c>
-      <c r="E512">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="F512">
-        <v>18.62</v>
-      </c>
-    </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A513" t="s">
-        <v>16</v>
-      </c>
-      <c r="B513" t="s">
-        <v>5</v>
-      </c>
-      <c r="C513">
-        <v>5</v>
-      </c>
-      <c r="D513" t="s">
-        <v>20</v>
-      </c>
-      <c r="E513">
-        <v>19.2</v>
-      </c>
-      <c r="F513">
-        <v>19.22</v>
-      </c>
-    </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A514" t="s">
-        <v>16</v>
-      </c>
-      <c r="B514" t="s">
-        <v>5</v>
-      </c>
-      <c r="C514">
-        <v>6</v>
-      </c>
-      <c r="D514" t="s">
-        <v>20</v>
-      </c>
-      <c r="E514">
-        <v>18.22</v>
-      </c>
-      <c r="F514">
-        <v>18.37</v>
-      </c>
-    </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A515" t="s">
-        <v>16</v>
-      </c>
-      <c r="B515" t="s">
-        <v>5</v>
-      </c>
-      <c r="C515">
-        <v>7</v>
-      </c>
-      <c r="D515" t="s">
-        <v>20</v>
-      </c>
-      <c r="E515">
-        <v>18.420000000000002</v>
-      </c>
-      <c r="F515">
-        <v>18.21</v>
-      </c>
-    </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A516" t="s">
-        <v>16</v>
-      </c>
-      <c r="B516" t="s">
-        <v>5</v>
-      </c>
-      <c r="C516">
-        <v>8</v>
-      </c>
-      <c r="D516" t="s">
-        <v>20</v>
-      </c>
-      <c r="E516">
-        <v>18.54</v>
-      </c>
-      <c r="F516">
-        <v>19.100000000000001</v>
-      </c>
-    </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A517" t="s">
-        <v>16</v>
-      </c>
-      <c r="B517" t="s">
-        <v>7</v>
-      </c>
-      <c r="C517">
-        <v>1</v>
-      </c>
-      <c r="D517" t="s">
-        <v>20</v>
-      </c>
-      <c r="E517">
-        <v>19.420000000000002</v>
-      </c>
-      <c r="F517">
-        <v>19.48</v>
-      </c>
-    </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A518" t="s">
-        <v>16</v>
-      </c>
-      <c r="B518" t="s">
-        <v>7</v>
-      </c>
-      <c r="C518">
-        <v>2</v>
-      </c>
-      <c r="D518" t="s">
-        <v>20</v>
-      </c>
-      <c r="E518">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="F518">
-        <v>18.149999999999999</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A519" t="s">
-        <v>16</v>
-      </c>
-      <c r="B519" t="s">
-        <v>7</v>
-      </c>
-      <c r="C519">
-        <v>3</v>
-      </c>
-      <c r="D519" t="s">
-        <v>20</v>
-      </c>
-      <c r="E519">
-        <v>18.77</v>
-      </c>
-      <c r="F519">
-        <v>18.88</v>
-      </c>
-    </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A520" t="s">
-        <v>16</v>
-      </c>
-      <c r="B520" t="s">
-        <v>7</v>
-      </c>
-      <c r="C520">
-        <v>4</v>
-      </c>
-      <c r="D520" t="s">
-        <v>20</v>
-      </c>
-      <c r="E520">
-        <v>20.91</v>
-      </c>
-      <c r="F520">
-        <v>20.41</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A521" t="s">
-        <v>16</v>
-      </c>
-      <c r="B521" t="s">
-        <v>7</v>
-      </c>
-      <c r="C521">
-        <v>5</v>
-      </c>
-      <c r="D521" t="s">
-        <v>20</v>
-      </c>
-      <c r="E521">
-        <v>19.16</v>
-      </c>
-      <c r="F521">
-        <v>18.23</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A522" t="s">
-        <v>16</v>
-      </c>
-      <c r="B522" t="s">
-        <v>7</v>
-      </c>
-      <c r="C522">
-        <v>6</v>
-      </c>
-      <c r="D522" t="s">
-        <v>20</v>
-      </c>
-      <c r="E522">
-        <v>19.22</v>
-      </c>
-      <c r="F522">
-        <v>19.27</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A523" t="s">
-        <v>16</v>
-      </c>
-      <c r="B523" t="s">
-        <v>7</v>
-      </c>
-      <c r="C523">
-        <v>7</v>
-      </c>
-      <c r="D523" t="s">
-        <v>20</v>
-      </c>
-      <c r="E523">
-        <v>18.09</v>
-      </c>
-      <c r="F523">
-        <v>18.190000000000001</v>
-      </c>
-    </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A524" t="s">
-        <v>16</v>
-      </c>
-      <c r="B524" t="s">
-        <v>8</v>
-      </c>
-      <c r="C524">
-        <v>1</v>
-      </c>
-      <c r="D524" t="s">
-        <v>20</v>
-      </c>
-      <c r="E524">
-        <v>17.510000000000002</v>
-      </c>
-      <c r="F524">
-        <v>17.329999999999998</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A525" t="s">
-        <v>16</v>
-      </c>
-      <c r="B525" t="s">
-        <v>8</v>
-      </c>
-      <c r="C525">
-        <v>2</v>
-      </c>
-      <c r="D525" t="s">
-        <v>20</v>
-      </c>
-      <c r="E525">
-        <v>18.010000000000002</v>
-      </c>
-      <c r="F525">
-        <v>18.670000000000002</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A526" t="s">
-        <v>16</v>
-      </c>
-      <c r="B526" t="s">
-        <v>8</v>
-      </c>
-      <c r="C526">
-        <v>3</v>
-      </c>
-      <c r="D526" t="s">
-        <v>20</v>
-      </c>
-      <c r="E526">
-        <v>18.25</v>
-      </c>
-      <c r="F526">
-        <v>18.87</v>
-      </c>
-    </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A527" t="s">
-        <v>16</v>
-      </c>
-      <c r="B527" t="s">
-        <v>8</v>
-      </c>
-      <c r="C527">
-        <v>4</v>
-      </c>
-      <c r="D527" t="s">
-        <v>20</v>
-      </c>
-      <c r="E527">
-        <v>18.940000000000001</v>
-      </c>
-      <c r="F527">
-        <v>18.73</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A528" t="s">
-        <v>16</v>
-      </c>
-      <c r="B528" t="s">
-        <v>8</v>
-      </c>
-      <c r="C528">
-        <v>5</v>
-      </c>
-      <c r="D528" t="s">
-        <v>20</v>
-      </c>
-      <c r="E528">
-        <v>18.97</v>
-      </c>
-      <c r="F528">
-        <v>18.41</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A529" t="s">
-        <v>16</v>
-      </c>
-      <c r="B529" t="s">
-        <v>8</v>
-      </c>
-      <c r="C529">
-        <v>6</v>
-      </c>
-      <c r="D529" t="s">
-        <v>20</v>
-      </c>
-      <c r="E529">
-        <v>18.2</v>
-      </c>
-      <c r="F529">
-        <v>18.02</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A530" t="s">
-        <v>16</v>
-      </c>
-      <c r="B530" t="s">
-        <v>8</v>
-      </c>
-      <c r="C530">
-        <v>7</v>
-      </c>
-      <c r="D530" t="s">
-        <v>20</v>
-      </c>
-      <c r="E530">
-        <v>17.579999999999998</v>
-      </c>
-      <c r="F530">
-        <v>17.62</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A531" t="s">
-        <v>16</v>
-      </c>
-      <c r="B531" t="s">
-        <v>8</v>
-      </c>
-      <c r="C531">
-        <v>8</v>
-      </c>
-      <c r="D531" t="s">
-        <v>20</v>
-      </c>
-      <c r="E531">
-        <v>17.07</v>
-      </c>
-      <c r="F531">
-        <v>17.46</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A532" t="s">
-        <v>16</v>
-      </c>
-      <c r="B532" t="s">
-        <v>9</v>
-      </c>
-      <c r="C532">
-        <v>1</v>
-      </c>
-      <c r="D532" t="s">
-        <v>20</v>
-      </c>
-      <c r="E532">
-        <v>21.01</v>
-      </c>
-      <c r="F532">
-        <v>20.49</v>
-      </c>
-    </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A533" t="s">
-        <v>16</v>
-      </c>
-      <c r="B533" t="s">
-        <v>9</v>
-      </c>
-      <c r="C533">
-        <v>2</v>
-      </c>
-      <c r="D533" t="s">
-        <v>20</v>
-      </c>
-      <c r="E533">
-        <v>17.23</v>
-      </c>
-      <c r="F533">
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A534" t="s">
-        <v>16</v>
-      </c>
-      <c r="B534" t="s">
-        <v>9</v>
-      </c>
-      <c r="C534">
-        <v>3</v>
-      </c>
-      <c r="D534" t="s">
-        <v>20</v>
-      </c>
-      <c r="E534">
-        <v>16.02</v>
-      </c>
-      <c r="F534">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A535" t="s">
-        <v>16</v>
-      </c>
-      <c r="B535" t="s">
-        <v>9</v>
-      </c>
-      <c r="C535">
-        <v>4</v>
-      </c>
-      <c r="D535" t="s">
-        <v>20</v>
-      </c>
-      <c r="E535">
-        <v>15.88</v>
-      </c>
-      <c r="F535">
-        <v>15.21</v>
-      </c>
-    </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A536" t="s">
-        <v>16</v>
-      </c>
-      <c r="B536" t="s">
-        <v>9</v>
-      </c>
-      <c r="C536">
-        <v>5</v>
-      </c>
-      <c r="D536" t="s">
-        <v>20</v>
-      </c>
-      <c r="E536">
-        <v>15.43</v>
-      </c>
-      <c r="F536">
-        <v>14.95</v>
-      </c>
-    </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A537" t="s">
-        <v>16</v>
-      </c>
-      <c r="B537" t="s">
-        <v>9</v>
-      </c>
-      <c r="C537">
-        <v>6</v>
-      </c>
-      <c r="D537" t="s">
-        <v>20</v>
-      </c>
-      <c r="E537">
-        <v>16.78</v>
-      </c>
-      <c r="F537">
-        <v>16.39</v>
-      </c>
-    </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A538" t="s">
-        <v>16</v>
-      </c>
-      <c r="B538" t="s">
-        <v>9</v>
-      </c>
-      <c r="C538">
-        <v>7</v>
-      </c>
-      <c r="D538" t="s">
-        <v>20</v>
-      </c>
-      <c r="E538">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="F538">
-        <v>18.489999999999998</v>
-      </c>
-    </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A539" t="s">
-        <v>16</v>
-      </c>
-      <c r="B539" t="s">
-        <v>9</v>
-      </c>
-      <c r="C539">
-        <v>8</v>
-      </c>
-      <c r="D539" t="s">
-        <v>20</v>
-      </c>
-      <c r="E539">
-        <v>15.94</v>
-      </c>
-      <c r="F539">
-        <v>15.97</v>
-      </c>
-    </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A540" t="s">
-        <v>16</v>
-      </c>
-      <c r="B540" t="s">
-        <v>10</v>
-      </c>
-      <c r="C540">
-        <v>1</v>
-      </c>
-      <c r="D540" t="s">
-        <v>20</v>
-      </c>
-      <c r="E540">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="F540">
-        <v>16.95</v>
-      </c>
-    </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A541" t="s">
-        <v>16</v>
-      </c>
-      <c r="B541" t="s">
-        <v>10</v>
-      </c>
-      <c r="C541">
-        <v>2</v>
-      </c>
-      <c r="D541" t="s">
-        <v>20</v>
-      </c>
-      <c r="E541">
-        <v>16.27</v>
-      </c>
-      <c r="F541">
-        <v>16.09</v>
-      </c>
-    </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A542" t="s">
-        <v>16</v>
-      </c>
-      <c r="B542" t="s">
-        <v>10</v>
-      </c>
-      <c r="C542">
-        <v>3</v>
-      </c>
-      <c r="D542" t="s">
-        <v>20</v>
-      </c>
-      <c r="E542">
-        <v>15.81</v>
-      </c>
-      <c r="F542">
-        <v>15.96</v>
-      </c>
-    </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A543" t="s">
-        <v>16</v>
-      </c>
-      <c r="B543" t="s">
-        <v>10</v>
-      </c>
-      <c r="C543">
-        <v>4</v>
-      </c>
-      <c r="D543" t="s">
-        <v>20</v>
-      </c>
-      <c r="E543">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="F543">
-        <v>16.329999999999998</v>
-      </c>
-    </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A544" t="s">
-        <v>16</v>
-      </c>
-      <c r="B544" t="s">
-        <v>10</v>
-      </c>
-      <c r="C544">
-        <v>5</v>
-      </c>
-      <c r="D544" t="s">
-        <v>20</v>
-      </c>
-      <c r="E544">
-        <v>16.079999999999998</v>
-      </c>
-      <c r="F544">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A545" t="s">
-        <v>16</v>
-      </c>
-      <c r="B545" t="s">
-        <v>10</v>
-      </c>
-      <c r="C545">
-        <v>6</v>
-      </c>
-      <c r="D545" t="s">
-        <v>20</v>
-      </c>
-      <c r="E545">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="F545">
-        <v>16.350000000000001</v>
-      </c>
-    </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A546" t="s">
-        <v>16</v>
-      </c>
-      <c r="B546" t="s">
-        <v>10</v>
-      </c>
-      <c r="C546">
-        <v>7</v>
-      </c>
-      <c r="D546" t="s">
-        <v>20</v>
-      </c>
-      <c r="E546">
-        <v>16.13</v>
-      </c>
-      <c r="F546">
-        <v>16.02</v>
-      </c>
-    </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A547" t="s">
-        <v>16</v>
-      </c>
-      <c r="B547" t="s">
-        <v>10</v>
-      </c>
-      <c r="C547">
-        <v>8</v>
-      </c>
-      <c r="D547" t="s">
-        <v>20</v>
-      </c>
-      <c r="E547">
-        <v>16.079999999999998</v>
-      </c>
-      <c r="F547">
-        <v>16.07</v>
-      </c>
-    </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A548" t="s">
-        <v>17</v>
-      </c>
-      <c r="B548" t="s">
-        <v>5</v>
-      </c>
-      <c r="C548">
-        <v>1</v>
-      </c>
-      <c r="D548" t="s">
-        <v>21</v>
-      </c>
-      <c r="E548">
-        <v>27.88</v>
-      </c>
-      <c r="F548">
-        <v>27.51</v>
-      </c>
-    </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A549" t="s">
-        <v>17</v>
-      </c>
-      <c r="B549" t="s">
-        <v>5</v>
-      </c>
-      <c r="C549">
-        <v>2</v>
-      </c>
-      <c r="D549" t="s">
-        <v>21</v>
-      </c>
-      <c r="E549">
-        <v>26.78</v>
-      </c>
-      <c r="F549">
-        <v>25.74</v>
-      </c>
-    </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A550" t="s">
-        <v>17</v>
-      </c>
-      <c r="B550" t="s">
-        <v>5</v>
-      </c>
-      <c r="C550">
-        <v>3</v>
-      </c>
-      <c r="D550" t="s">
-        <v>21</v>
-      </c>
-      <c r="E550">
-        <v>26.03</v>
-      </c>
-      <c r="F550">
-        <v>26.05</v>
-      </c>
-    </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A551" t="s">
-        <v>17</v>
-      </c>
-      <c r="B551" t="s">
-        <v>5</v>
-      </c>
-      <c r="C551">
-        <v>4</v>
-      </c>
-      <c r="D551" t="s">
-        <v>21</v>
-      </c>
-      <c r="E551">
-        <v>25.41</v>
-      </c>
-      <c r="F551">
-        <v>25.73</v>
-      </c>
-    </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A552" t="s">
-        <v>17</v>
-      </c>
-      <c r="B552" t="s">
-        <v>5</v>
-      </c>
-      <c r="C552">
-        <v>5</v>
-      </c>
-      <c r="D552" t="s">
-        <v>21</v>
-      </c>
-      <c r="E552">
-        <v>25.61</v>
-      </c>
-      <c r="F552">
-        <v>26.03</v>
-      </c>
-    </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A553" t="s">
-        <v>17</v>
-      </c>
-      <c r="B553" t="s">
-        <v>5</v>
-      </c>
-      <c r="C553">
-        <v>6</v>
-      </c>
-      <c r="D553" t="s">
-        <v>21</v>
-      </c>
-      <c r="E553">
-        <v>25.78</v>
-      </c>
-      <c r="F553">
-        <v>25.15</v>
-      </c>
-    </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A554" t="s">
-        <v>17</v>
-      </c>
-      <c r="B554" t="s">
-        <v>5</v>
-      </c>
-      <c r="C554">
-        <v>7</v>
-      </c>
-      <c r="D554" t="s">
-        <v>21</v>
-      </c>
-      <c r="E554">
-        <v>25.3</v>
-      </c>
-      <c r="F554">
-        <v>24.3</v>
-      </c>
-    </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A555" t="s">
-        <v>17</v>
-      </c>
-      <c r="B555" t="s">
-        <v>5</v>
-      </c>
-      <c r="C555">
-        <v>8</v>
-      </c>
-      <c r="D555" t="s">
-        <v>21</v>
-      </c>
-      <c r="E555">
-        <v>24.99</v>
-      </c>
-      <c r="F555">
-        <v>25.75</v>
-      </c>
-    </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A556" t="s">
-        <v>17</v>
-      </c>
-      <c r="B556" t="s">
-        <v>7</v>
-      </c>
-      <c r="C556">
-        <v>1</v>
-      </c>
-      <c r="D556" t="s">
-        <v>21</v>
-      </c>
-      <c r="E556">
-        <v>26.36</v>
-      </c>
-      <c r="F556">
-        <v>26.89</v>
-      </c>
-    </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A557" t="s">
-        <v>17</v>
-      </c>
-      <c r="B557" t="s">
-        <v>7</v>
-      </c>
-      <c r="C557">
-        <v>2</v>
-      </c>
-      <c r="D557" t="s">
-        <v>21</v>
-      </c>
-      <c r="E557">
-        <v>26.97</v>
-      </c>
-      <c r="F557">
-        <v>26.94</v>
-      </c>
-    </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A558" t="s">
-        <v>17</v>
-      </c>
-      <c r="B558" t="s">
-        <v>7</v>
-      </c>
-      <c r="C558">
-        <v>3</v>
-      </c>
-      <c r="D558" t="s">
-        <v>21</v>
-      </c>
-      <c r="E558">
-        <v>26.39</v>
-      </c>
-      <c r="F558">
-        <v>26.67</v>
-      </c>
-    </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A559" t="s">
-        <v>17</v>
-      </c>
-      <c r="B559" t="s">
-        <v>7</v>
-      </c>
-      <c r="C559">
-        <v>4</v>
-      </c>
-      <c r="D559" t="s">
-        <v>21</v>
-      </c>
-      <c r="E559">
-        <v>25.43</v>
-      </c>
-      <c r="F559">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A560" t="s">
-        <v>17</v>
-      </c>
-      <c r="B560" t="s">
-        <v>7</v>
-      </c>
-      <c r="C560">
-        <v>5</v>
-      </c>
-      <c r="D560" t="s">
-        <v>21</v>
-      </c>
-      <c r="E560">
-        <v>24.74</v>
-      </c>
-      <c r="F560">
-        <v>24.24</v>
-      </c>
-    </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A561" t="s">
-        <v>17</v>
-      </c>
-      <c r="B561" t="s">
-        <v>7</v>
-      </c>
-      <c r="C561">
-        <v>6</v>
-      </c>
-      <c r="D561" t="s">
-        <v>21</v>
-      </c>
-      <c r="E561">
-        <v>25.67</v>
-      </c>
-      <c r="F561">
-        <v>25.47</v>
-      </c>
-    </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A562" t="s">
-        <v>17</v>
-      </c>
-      <c r="B562" t="s">
-        <v>7</v>
-      </c>
-      <c r="C562">
-        <v>7</v>
-      </c>
-      <c r="D562" t="s">
-        <v>21</v>
-      </c>
-      <c r="E562">
-        <v>26.68</v>
-      </c>
-      <c r="F562">
-        <v>26.18</v>
-      </c>
-    </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A563" t="s">
-        <v>17</v>
-      </c>
-      <c r="B563" t="s">
-        <v>8</v>
-      </c>
-      <c r="C563">
-        <v>1</v>
-      </c>
-      <c r="D563" t="s">
-        <v>21</v>
-      </c>
-      <c r="E563">
-        <v>26.27</v>
-      </c>
-      <c r="F563">
-        <v>26.45</v>
-      </c>
-    </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A564" t="s">
-        <v>17</v>
-      </c>
-      <c r="B564" t="s">
-        <v>8</v>
-      </c>
-      <c r="C564">
-        <v>2</v>
-      </c>
-      <c r="D564" t="s">
-        <v>21</v>
-      </c>
-      <c r="E564">
-        <v>25.42</v>
-      </c>
-      <c r="F564">
-        <v>25.53</v>
-      </c>
-    </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A565" t="s">
-        <v>17</v>
-      </c>
-      <c r="B565" t="s">
-        <v>8</v>
-      </c>
-      <c r="C565">
-        <v>3</v>
-      </c>
-      <c r="D565" t="s">
-        <v>21</v>
-      </c>
-      <c r="E565">
-        <v>25.73</v>
-      </c>
-      <c r="F565">
-        <v>26.08</v>
-      </c>
-    </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A566" t="s">
-        <v>17</v>
-      </c>
-      <c r="B566" t="s">
-        <v>8</v>
-      </c>
-      <c r="C566">
-        <v>4</v>
-      </c>
-      <c r="D566" t="s">
-        <v>21</v>
-      </c>
-      <c r="E566">
-        <v>26.77</v>
-      </c>
-      <c r="F566">
-        <v>26.89</v>
-      </c>
-    </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A567" t="s">
-        <v>17</v>
-      </c>
-      <c r="B567" t="s">
-        <v>8</v>
-      </c>
-      <c r="C567">
-        <v>5</v>
-      </c>
-      <c r="D567" t="s">
-        <v>21</v>
-      </c>
-      <c r="E567">
-        <v>26.27</v>
-      </c>
-      <c r="F567">
-        <v>27.04</v>
-      </c>
-    </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A568" t="s">
-        <v>17</v>
-      </c>
-      <c r="B568" t="s">
-        <v>8</v>
-      </c>
-      <c r="C568">
-        <v>6</v>
-      </c>
-      <c r="D568" t="s">
-        <v>21</v>
-      </c>
-      <c r="E568">
-        <v>25.42</v>
-      </c>
-      <c r="F568">
-        <v>25.78</v>
-      </c>
-    </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A569" t="s">
-        <v>17</v>
-      </c>
-      <c r="B569" t="s">
-        <v>8</v>
-      </c>
-      <c r="C569">
-        <v>7</v>
-      </c>
-      <c r="D569" t="s">
-        <v>21</v>
-      </c>
-      <c r="E569">
-        <v>26.62</v>
-      </c>
-      <c r="F569">
-        <v>26.95</v>
-      </c>
-    </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A570" t="s">
-        <v>17</v>
-      </c>
-      <c r="B570" t="s">
-        <v>8</v>
-      </c>
-      <c r="C570">
-        <v>8</v>
-      </c>
-      <c r="D570" t="s">
-        <v>21</v>
-      </c>
-      <c r="E570">
-        <v>25.97</v>
-      </c>
-      <c r="F570">
-        <v>25.36</v>
-      </c>
-    </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A571" t="s">
-        <v>17</v>
-      </c>
-      <c r="B571" t="s">
-        <v>9</v>
-      </c>
-      <c r="C571">
-        <v>1</v>
-      </c>
-      <c r="D571" t="s">
-        <v>21</v>
-      </c>
-      <c r="E571">
-        <v>25.33</v>
-      </c>
-      <c r="F571">
-        <v>25.68</v>
-      </c>
-    </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A572" t="s">
-        <v>17</v>
-      </c>
-      <c r="B572" t="s">
-        <v>9</v>
-      </c>
-      <c r="C572">
-        <v>2</v>
-      </c>
-      <c r="D572" t="s">
-        <v>21</v>
-      </c>
-      <c r="E572">
-        <v>26.14</v>
-      </c>
-      <c r="F572">
-        <v>25.07</v>
-      </c>
-    </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A573" t="s">
-        <v>17</v>
-      </c>
-      <c r="B573" t="s">
-        <v>9</v>
-      </c>
-      <c r="C573">
-        <v>3</v>
-      </c>
-      <c r="D573" t="s">
-        <v>21</v>
-      </c>
-      <c r="E573">
-        <v>27.1</v>
-      </c>
-      <c r="F573">
-        <v>26.8</v>
-      </c>
-    </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A574" t="s">
-        <v>17</v>
-      </c>
-      <c r="B574" t="s">
-        <v>9</v>
-      </c>
-      <c r="C574">
-        <v>4</v>
-      </c>
-      <c r="D574" t="s">
-        <v>21</v>
-      </c>
-      <c r="E574">
-        <v>24.66</v>
-      </c>
-      <c r="F574">
-        <v>24.27</v>
-      </c>
-    </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A575" t="s">
-        <v>17</v>
-      </c>
-      <c r="B575" t="s">
-        <v>9</v>
-      </c>
-      <c r="C575">
-        <v>5</v>
-      </c>
-      <c r="D575" t="s">
-        <v>21</v>
-      </c>
-      <c r="E575">
-        <v>26.67</v>
-      </c>
-      <c r="F575">
-        <v>26.35</v>
-      </c>
-    </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A576" t="s">
-        <v>17</v>
-      </c>
-      <c r="B576" t="s">
-        <v>9</v>
-      </c>
-      <c r="C576">
-        <v>6</v>
-      </c>
-      <c r="D576" t="s">
-        <v>21</v>
-      </c>
-      <c r="E576">
-        <v>26.17</v>
-      </c>
-      <c r="F576">
-        <v>26.22</v>
-      </c>
-    </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A577" t="s">
-        <v>17</v>
-      </c>
-      <c r="B577" t="s">
-        <v>9</v>
-      </c>
-      <c r="C577">
-        <v>7</v>
-      </c>
-      <c r="D577" t="s">
-        <v>21</v>
-      </c>
-      <c r="E577">
-        <v>26.89</v>
-      </c>
-      <c r="F577">
-        <v>26.49</v>
-      </c>
-    </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A578" t="s">
-        <v>17</v>
-      </c>
-      <c r="B578" t="s">
-        <v>9</v>
-      </c>
-      <c r="C578">
-        <v>8</v>
-      </c>
-      <c r="D578" t="s">
-        <v>21</v>
-      </c>
-      <c r="E578">
-        <v>25.67</v>
-      </c>
-      <c r="F578">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A579" t="s">
-        <v>17</v>
-      </c>
-      <c r="B579" t="s">
-        <v>10</v>
-      </c>
-      <c r="C579">
-        <v>1</v>
-      </c>
-      <c r="D579" t="s">
-        <v>21</v>
-      </c>
-      <c r="E579">
-        <v>25.11</v>
-      </c>
-      <c r="F579">
-        <v>25.78</v>
-      </c>
-    </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A580" t="s">
-        <v>17</v>
-      </c>
-      <c r="B580" t="s">
-        <v>10</v>
-      </c>
-      <c r="C580">
-        <v>2</v>
-      </c>
-      <c r="D580" t="s">
-        <v>21</v>
-      </c>
-      <c r="E580">
-        <v>22.3</v>
-      </c>
-      <c r="F580">
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A581" t="s">
-        <v>17</v>
-      </c>
-      <c r="B581" t="s">
-        <v>10</v>
-      </c>
-      <c r="C581">
-        <v>3</v>
-      </c>
-      <c r="D581" t="s">
-        <v>21</v>
-      </c>
-      <c r="E581">
-        <v>24.02</v>
-      </c>
-      <c r="F581">
-        <v>23.12</v>
-      </c>
-    </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A582" t="s">
-        <v>17</v>
-      </c>
-      <c r="B582" t="s">
-        <v>10</v>
-      </c>
-      <c r="C582">
-        <v>4</v>
-      </c>
-      <c r="D582" t="s">
-        <v>21</v>
-      </c>
-      <c r="E582">
-        <v>24.83</v>
-      </c>
-      <c r="F582">
-        <v>24.83</v>
-      </c>
-    </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A583" t="s">
-        <v>17</v>
-      </c>
-      <c r="B583" t="s">
-        <v>10</v>
-      </c>
-      <c r="C583">
-        <v>5</v>
-      </c>
-      <c r="D583" t="s">
-        <v>21</v>
-      </c>
-      <c r="E583">
-        <v>25.38</v>
-      </c>
-      <c r="F583">
-        <v>25.01</v>
-      </c>
-    </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A584" t="s">
-        <v>17</v>
-      </c>
-      <c r="B584" t="s">
-        <v>10</v>
-      </c>
-      <c r="C584">
-        <v>6</v>
-      </c>
-      <c r="D584" t="s">
-        <v>21</v>
-      </c>
-      <c r="E584">
-        <v>27.68</v>
-      </c>
-      <c r="F584">
-        <v>27.2</v>
-      </c>
-    </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A585" t="s">
-        <v>17</v>
-      </c>
-      <c r="B585" t="s">
-        <v>10</v>
-      </c>
-      <c r="C585">
-        <v>7</v>
-      </c>
-      <c r="D585" t="s">
-        <v>21</v>
-      </c>
-      <c r="E585">
-        <v>26.11</v>
-      </c>
-      <c r="F585">
-        <v>26.62</v>
-      </c>
-    </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A586" t="s">
-        <v>17</v>
-      </c>
-      <c r="B586" t="s">
-        <v>10</v>
-      </c>
-      <c r="C586">
-        <v>8</v>
-      </c>
-      <c r="D586" t="s">
-        <v>21</v>
-      </c>
-      <c r="E586">
-        <v>23.72</v>
-      </c>
-      <c r="F586">
-        <v>22.78</v>
-      </c>
-    </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A587" t="s">
-        <v>17</v>
-      </c>
-      <c r="B587" t="s">
-        <v>5</v>
-      </c>
-      <c r="C587">
-        <v>1</v>
-      </c>
-      <c r="D587" t="s">
-        <v>22</v>
-      </c>
-      <c r="E587">
-        <v>28.72</v>
-      </c>
-      <c r="F587">
-        <v>29.23</v>
-      </c>
-    </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A588" t="s">
-        <v>17</v>
-      </c>
-      <c r="B588" t="s">
-        <v>5</v>
-      </c>
-      <c r="C588">
-        <v>2</v>
-      </c>
-      <c r="D588" t="s">
-        <v>22</v>
-      </c>
-      <c r="E588">
-        <v>27.1</v>
-      </c>
-      <c r="F588">
-        <v>27.32</v>
-      </c>
-    </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A589" t="s">
-        <v>17</v>
-      </c>
-      <c r="B589" t="s">
-        <v>5</v>
-      </c>
-      <c r="C589">
-        <v>3</v>
-      </c>
-      <c r="D589" t="s">
-        <v>22</v>
-      </c>
-      <c r="E589">
-        <v>26.29</v>
-      </c>
-      <c r="F589">
-        <v>26.75</v>
-      </c>
-    </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A590" t="s">
-        <v>17</v>
-      </c>
-      <c r="B590" t="s">
-        <v>5</v>
-      </c>
-      <c r="C590">
-        <v>4</v>
-      </c>
-      <c r="D590" t="s">
-        <v>22</v>
-      </c>
-      <c r="E590">
-        <v>25.61</v>
-      </c>
-      <c r="F590">
-        <v>25.39</v>
-      </c>
-    </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A591" t="s">
-        <v>17</v>
-      </c>
-      <c r="B591" t="s">
-        <v>5</v>
-      </c>
-      <c r="C591">
-        <v>5</v>
-      </c>
-      <c r="D591" t="s">
-        <v>22</v>
-      </c>
-      <c r="E591">
-        <v>25.55</v>
-      </c>
-      <c r="F591">
-        <v>25.82</v>
-      </c>
-    </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A592" t="s">
-        <v>17</v>
-      </c>
-      <c r="B592" t="s">
-        <v>5</v>
-      </c>
-      <c r="C592">
-        <v>6</v>
-      </c>
-      <c r="D592" t="s">
-        <v>22</v>
-      </c>
-      <c r="E592">
-        <v>25.51</v>
-      </c>
-      <c r="F592">
-        <v>25.53</v>
-      </c>
-    </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A593" t="s">
-        <v>17</v>
-      </c>
-      <c r="B593" t="s">
-        <v>5</v>
-      </c>
-      <c r="C593">
-        <v>7</v>
-      </c>
-      <c r="D593" t="s">
-        <v>22</v>
-      </c>
-      <c r="E593">
-        <v>23.95</v>
-      </c>
-      <c r="F593">
-        <v>24.98</v>
-      </c>
-    </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A594" t="s">
-        <v>17</v>
-      </c>
-      <c r="B594" t="s">
-        <v>5</v>
-      </c>
-      <c r="C594">
-        <v>8</v>
-      </c>
-      <c r="D594" t="s">
-        <v>22</v>
-      </c>
-      <c r="E594">
-        <v>25.39</v>
-      </c>
-      <c r="F594">
-        <v>25.47</v>
-      </c>
-    </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A595" t="s">
-        <v>17</v>
-      </c>
-      <c r="B595" t="s">
-        <v>7</v>
-      </c>
-      <c r="C595">
-        <v>1</v>
-      </c>
-      <c r="D595" t="s">
-        <v>22</v>
-      </c>
-      <c r="E595">
-        <v>27.94</v>
-      </c>
-      <c r="F595">
-        <v>27.98</v>
-      </c>
-    </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A596" t="s">
-        <v>17</v>
-      </c>
-      <c r="B596" t="s">
-        <v>7</v>
-      </c>
-      <c r="C596">
-        <v>2</v>
-      </c>
-      <c r="D596" t="s">
-        <v>22</v>
-      </c>
-      <c r="E596">
-        <v>27.65</v>
-      </c>
-      <c r="F596">
-        <v>27.45</v>
-      </c>
-    </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A597" t="s">
-        <v>17</v>
-      </c>
-      <c r="B597" t="s">
-        <v>7</v>
-      </c>
-      <c r="C597">
-        <v>3</v>
-      </c>
-      <c r="D597" t="s">
-        <v>22</v>
-      </c>
-      <c r="E597">
-        <v>27.52</v>
-      </c>
-      <c r="F597">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A598" t="s">
-        <v>17</v>
-      </c>
-      <c r="B598" t="s">
-        <v>7</v>
-      </c>
-      <c r="C598">
-        <v>4</v>
-      </c>
-      <c r="D598" t="s">
-        <v>22</v>
-      </c>
-      <c r="E598">
-        <v>26.17</v>
-      </c>
-      <c r="F598">
-        <v>26.23</v>
-      </c>
-    </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A599" t="s">
-        <v>17</v>
-      </c>
-      <c r="B599" t="s">
-        <v>7</v>
-      </c>
-      <c r="C599">
-        <v>5</v>
-      </c>
-      <c r="D599" t="s">
-        <v>22</v>
-      </c>
-      <c r="E599">
-        <v>26.87</v>
-      </c>
-      <c r="F599">
-        <v>27.05</v>
-      </c>
-    </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A600" t="s">
-        <v>17</v>
-      </c>
-      <c r="B600" t="s">
-        <v>7</v>
-      </c>
-      <c r="C600">
-        <v>6</v>
-      </c>
-      <c r="D600" t="s">
-        <v>22</v>
-      </c>
-      <c r="E600">
-        <v>27.6</v>
-      </c>
-      <c r="F600">
-        <v>27.37</v>
-      </c>
-    </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A601" t="s">
-        <v>17</v>
-      </c>
-      <c r="B601" t="s">
-        <v>7</v>
-      </c>
-      <c r="C601">
-        <v>7</v>
-      </c>
-      <c r="D601" t="s">
-        <v>22</v>
-      </c>
-      <c r="E601">
-        <v>27.4</v>
-      </c>
-      <c r="F601">
-        <v>27.12</v>
-      </c>
-    </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A602" t="s">
-        <v>17</v>
-      </c>
-      <c r="B602" t="s">
-        <v>8</v>
-      </c>
-      <c r="C602">
-        <v>1</v>
-      </c>
-      <c r="D602" t="s">
-        <v>22</v>
-      </c>
-      <c r="E602">
-        <v>26.83</v>
-      </c>
-      <c r="F602">
-        <v>26.94</v>
-      </c>
-    </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A603" t="s">
-        <v>17</v>
-      </c>
-      <c r="B603" t="s">
-        <v>8</v>
-      </c>
-      <c r="C603">
-        <v>2</v>
-      </c>
-      <c r="D603" t="s">
-        <v>22</v>
-      </c>
-      <c r="E603">
-        <v>26.22</v>
-      </c>
-      <c r="F603">
-        <v>26.07</v>
-      </c>
-    </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A604" t="s">
-        <v>17</v>
-      </c>
-      <c r="B604" t="s">
-        <v>8</v>
-      </c>
-      <c r="C604">
-        <v>3</v>
-      </c>
-      <c r="D604" t="s">
-        <v>22</v>
-      </c>
-      <c r="E604">
-        <v>26.26</v>
-      </c>
-      <c r="F604">
-        <v>26.69</v>
-      </c>
-    </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A605" t="s">
-        <v>17</v>
-      </c>
-      <c r="B605" t="s">
-        <v>8</v>
-      </c>
-      <c r="C605">
-        <v>4</v>
-      </c>
-      <c r="D605" t="s">
-        <v>22</v>
-      </c>
-      <c r="E605">
-        <v>28.03</v>
-      </c>
-      <c r="F605">
-        <v>28.06</v>
-      </c>
-    </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A606" t="s">
-        <v>17</v>
-      </c>
-      <c r="B606" t="s">
-        <v>8</v>
-      </c>
-      <c r="C606">
-        <v>5</v>
-      </c>
-      <c r="D606" t="s">
-        <v>22</v>
-      </c>
-      <c r="E606">
-        <v>27.3</v>
-      </c>
-      <c r="F606">
-        <v>27.9</v>
-      </c>
-    </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A607" t="s">
-        <v>17</v>
-      </c>
-      <c r="B607" t="s">
-        <v>8</v>
-      </c>
-      <c r="C607">
-        <v>6</v>
-      </c>
-      <c r="D607" t="s">
-        <v>22</v>
-      </c>
-      <c r="E607">
-        <v>27.78</v>
-      </c>
-      <c r="F607">
-        <v>27.77</v>
-      </c>
-    </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A608" t="s">
-        <v>17</v>
-      </c>
-      <c r="B608" t="s">
-        <v>8</v>
-      </c>
-      <c r="C608">
-        <v>7</v>
-      </c>
-      <c r="D608" t="s">
-        <v>22</v>
-      </c>
-      <c r="E608">
-        <v>28.54</v>
-      </c>
-      <c r="F608">
-        <v>28.4</v>
-      </c>
-    </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A609" t="s">
-        <v>17</v>
-      </c>
-      <c r="B609" t="s">
-        <v>8</v>
-      </c>
-      <c r="C609">
-        <v>8</v>
-      </c>
-      <c r="D609" t="s">
-        <v>22</v>
-      </c>
-      <c r="E609">
-        <v>26.27</v>
-      </c>
-      <c r="F609">
-        <v>26.19</v>
-      </c>
-    </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A610" t="s">
-        <v>17</v>
-      </c>
-      <c r="B610" t="s">
-        <v>9</v>
-      </c>
-      <c r="C610">
-        <v>1</v>
-      </c>
-      <c r="D610" t="s">
-        <v>22</v>
-      </c>
-      <c r="E610">
-        <v>26.73</v>
-      </c>
-      <c r="F610">
-        <v>26.82</v>
-      </c>
-    </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A611" t="s">
-        <v>17</v>
-      </c>
-      <c r="B611" t="s">
-        <v>9</v>
-      </c>
-      <c r="C611">
-        <v>2</v>
-      </c>
-      <c r="D611" t="s">
-        <v>22</v>
-      </c>
-      <c r="E611">
-        <v>26.04</v>
-      </c>
-      <c r="F611">
-        <v>25.93</v>
-      </c>
-    </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A612" t="s">
-        <v>17</v>
-      </c>
-      <c r="B612" t="s">
-        <v>9</v>
-      </c>
-      <c r="C612">
-        <v>3</v>
-      </c>
-      <c r="D612" t="s">
-        <v>22</v>
-      </c>
-      <c r="E612">
-        <v>28.41</v>
-      </c>
-      <c r="F612">
-        <v>27.8</v>
-      </c>
-    </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A613" t="s">
-        <v>17</v>
-      </c>
-      <c r="B613" t="s">
-        <v>9</v>
-      </c>
-      <c r="C613">
-        <v>4</v>
-      </c>
-      <c r="D613" t="s">
-        <v>22</v>
-      </c>
-      <c r="E613">
-        <v>25</v>
-      </c>
-      <c r="F613">
-        <v>24.93</v>
-      </c>
-    </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A614" t="s">
-        <v>17</v>
-      </c>
-      <c r="B614" t="s">
-        <v>9</v>
-      </c>
-      <c r="C614">
-        <v>5</v>
-      </c>
-      <c r="D614" t="s">
-        <v>22</v>
-      </c>
-      <c r="E614">
-        <v>27.06</v>
-      </c>
-      <c r="F614">
-        <v>27.45</v>
-      </c>
-    </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A615" t="s">
-        <v>17</v>
-      </c>
-      <c r="B615" t="s">
-        <v>9</v>
-      </c>
-      <c r="C615">
-        <v>6</v>
-      </c>
-      <c r="D615" t="s">
-        <v>22</v>
-      </c>
-      <c r="E615">
-        <v>26.7</v>
-      </c>
-      <c r="F615">
-        <v>26.47</v>
-      </c>
-    </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A616" t="s">
-        <v>17</v>
-      </c>
-      <c r="B616" t="s">
-        <v>9</v>
-      </c>
-      <c r="C616">
-        <v>7</v>
-      </c>
-      <c r="D616" t="s">
-        <v>22</v>
-      </c>
-      <c r="E616">
-        <v>26.54</v>
-      </c>
-      <c r="F616">
-        <v>26.57</v>
-      </c>
-    </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A617" t="s">
-        <v>17</v>
-      </c>
-      <c r="B617" t="s">
-        <v>9</v>
-      </c>
-      <c r="C617">
-        <v>8</v>
-      </c>
-      <c r="D617" t="s">
-        <v>22</v>
-      </c>
-      <c r="E617">
-        <v>26.44</v>
-      </c>
-      <c r="F617">
-        <v>26.58</v>
-      </c>
-    </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A618" t="s">
-        <v>17</v>
-      </c>
-      <c r="B618" t="s">
-        <v>10</v>
-      </c>
-      <c r="C618">
-        <v>1</v>
-      </c>
-      <c r="D618" t="s">
-        <v>22</v>
-      </c>
-      <c r="E618">
-        <v>25.48</v>
-      </c>
-      <c r="F618">
-        <v>25.51</v>
-      </c>
-    </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A619" t="s">
-        <v>17</v>
-      </c>
-      <c r="B619" t="s">
-        <v>10</v>
-      </c>
-      <c r="C619">
-        <v>2</v>
-      </c>
-      <c r="D619" t="s">
-        <v>22</v>
-      </c>
-      <c r="E619">
-        <v>24.51</v>
-      </c>
-      <c r="F619">
-        <v>24.74</v>
-      </c>
-    </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A620" t="s">
-        <v>17</v>
-      </c>
-      <c r="B620" t="s">
-        <v>10</v>
-      </c>
-      <c r="C620">
-        <v>3</v>
-      </c>
-      <c r="D620" t="s">
-        <v>22</v>
-      </c>
-      <c r="E620">
-        <v>25.74</v>
-      </c>
-      <c r="F620">
-        <v>26.03</v>
-      </c>
-    </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A621" t="s">
-        <v>17</v>
-      </c>
-      <c r="B621" t="s">
-        <v>10</v>
-      </c>
-      <c r="C621">
-        <v>4</v>
-      </c>
-      <c r="D621" t="s">
-        <v>22</v>
-      </c>
-      <c r="E621">
-        <v>25.8</v>
-      </c>
-      <c r="F621">
-        <v>25.67</v>
-      </c>
-    </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A622" t="s">
-        <v>17</v>
-      </c>
-      <c r="B622" t="s">
-        <v>10</v>
-      </c>
-      <c r="C622">
-        <v>5</v>
-      </c>
-      <c r="D622" t="s">
-        <v>22</v>
-      </c>
-      <c r="E622">
-        <v>26.13</v>
-      </c>
-      <c r="F622">
-        <v>26.01</v>
-      </c>
-    </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A623" t="s">
-        <v>17</v>
-      </c>
-      <c r="B623" t="s">
-        <v>10</v>
-      </c>
-      <c r="C623">
-        <v>6</v>
-      </c>
-      <c r="D623" t="s">
-        <v>22</v>
-      </c>
-      <c r="E623">
-        <v>27.78</v>
-      </c>
-      <c r="F623">
-        <v>28.03</v>
-      </c>
-    </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A624" t="s">
-        <v>17</v>
-      </c>
-      <c r="B624" t="s">
-        <v>10</v>
-      </c>
-      <c r="C624">
-        <v>7</v>
-      </c>
-      <c r="D624" t="s">
-        <v>22</v>
-      </c>
-      <c r="E624">
-        <v>29.2</v>
-      </c>
-      <c r="F624">
-        <v>28.77</v>
-      </c>
-    </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A625" t="s">
-        <v>17</v>
-      </c>
-      <c r="B625" t="s">
-        <v>10</v>
-      </c>
-      <c r="C625">
-        <v>8</v>
-      </c>
-      <c r="D625" t="s">
-        <v>22</v>
-      </c>
-      <c r="E625">
-        <v>25.92</v>
-      </c>
-      <c r="F625">
-        <v>25.75</v>
-      </c>
-    </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A626" t="s">
-        <v>16</v>
-      </c>
-      <c r="B626" t="s">
-        <v>5</v>
-      </c>
-      <c r="C626">
-        <v>1</v>
-      </c>
-      <c r="D626" t="s">
-        <v>25</v>
-      </c>
-      <c r="E626" s="1">
-        <v>28.053165621050098</v>
-      </c>
-      <c r="F626" s="1">
-        <v>28.0857390978917</v>
-      </c>
-    </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A627" t="s">
-        <v>16</v>
-      </c>
-      <c r="B627" t="s">
-        <v>5</v>
-      </c>
-      <c r="C627">
-        <v>2</v>
-      </c>
-      <c r="D627" t="s">
-        <v>25</v>
-      </c>
-      <c r="E627" s="1">
-        <v>30.0503992850206</v>
-      </c>
-      <c r="F627" s="1">
-        <v>29.914640295490202</v>
-      </c>
-    </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A628" t="s">
-        <v>16</v>
-      </c>
-      <c r="B628" t="s">
-        <v>5</v>
-      </c>
-      <c r="C628">
-        <v>3</v>
-      </c>
-      <c r="D628" t="s">
-        <v>25</v>
-      </c>
-      <c r="E628" s="1">
-        <v>28.808130776376899</v>
-      </c>
-      <c r="F628" s="1">
-        <v>28.576923817220301</v>
-      </c>
-    </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A629" t="s">
-        <v>16</v>
-      </c>
-      <c r="B629" t="s">
-        <v>5</v>
-      </c>
-      <c r="C629">
-        <v>4</v>
-      </c>
-      <c r="D629" t="s">
-        <v>25</v>
-      </c>
-      <c r="E629" s="1">
-        <v>28.284978647312801</v>
-      </c>
-      <c r="F629" s="1">
-        <v>27.3132014966417</v>
-      </c>
-    </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A630" t="s">
-        <v>16</v>
-      </c>
-      <c r="B630" t="s">
-        <v>5</v>
-      </c>
-      <c r="C630">
-        <v>5</v>
-      </c>
-      <c r="D630" t="s">
-        <v>25</v>
-      </c>
-      <c r="E630" s="1">
-        <v>30.390326192228802</v>
-      </c>
-      <c r="F630" s="1">
-        <v>30.485760002632802</v>
-      </c>
-    </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A631" t="s">
-        <v>16</v>
-      </c>
-      <c r="B631" t="s">
-        <v>5</v>
-      </c>
-      <c r="C631">
-        <v>6</v>
-      </c>
-      <c r="D631" t="s">
-        <v>25</v>
-      </c>
-      <c r="E631" s="1">
-        <v>29.053738371678801</v>
-      </c>
-      <c r="F631" s="1">
-        <v>29.515994767132401</v>
-      </c>
-    </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A632" t="s">
-        <v>16</v>
-      </c>
-      <c r="B632" t="s">
-        <v>5</v>
-      </c>
-      <c r="C632">
-        <v>7</v>
-      </c>
-      <c r="D632" t="s">
-        <v>25</v>
-      </c>
-      <c r="E632" s="1">
-        <v>29.1718625422718</v>
-      </c>
-      <c r="F632" s="1">
-        <v>29.363604750268301</v>
-      </c>
-    </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A633" t="s">
-        <v>16</v>
-      </c>
-      <c r="B633" t="s">
-        <v>5</v>
-      </c>
-      <c r="C633">
-        <v>8</v>
-      </c>
-      <c r="D633" t="s">
-        <v>25</v>
-      </c>
-      <c r="E633" s="1">
-        <v>28.992182255112901</v>
-      </c>
-      <c r="F633" s="1">
-        <v>29.415704724209</v>
-      </c>
-    </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A634" t="s">
-        <v>16</v>
-      </c>
-      <c r="B634" t="s">
-        <v>7</v>
-      </c>
-      <c r="C634">
-        <v>1</v>
-      </c>
-      <c r="D634" t="s">
-        <v>25</v>
-      </c>
-      <c r="E634" s="1">
-        <v>29.762943796644201</v>
-      </c>
-      <c r="F634" s="1">
-        <v>30.124111744582098</v>
-      </c>
-    </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A635" t="s">
-        <v>16</v>
-      </c>
-      <c r="B635" t="s">
-        <v>7</v>
-      </c>
-      <c r="C635">
-        <v>2</v>
-      </c>
-      <c r="D635" t="s">
-        <v>25</v>
-      </c>
-      <c r="E635" s="1">
-        <v>29.003592063641801</v>
-      </c>
-      <c r="F635" s="1">
-        <v>28.430701827647901</v>
-      </c>
-    </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A636" t="s">
-        <v>16</v>
-      </c>
-      <c r="B636" t="s">
-        <v>7</v>
-      </c>
-      <c r="C636">
-        <v>3</v>
-      </c>
-      <c r="D636" t="s">
-        <v>25</v>
-      </c>
-      <c r="E636" s="1">
-        <v>29.5501513232619</v>
-      </c>
-      <c r="F636" s="1">
-        <v>30.608154623024401</v>
-      </c>
-    </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A637" t="s">
-        <v>16</v>
-      </c>
-      <c r="B637" t="s">
-        <v>7</v>
-      </c>
-      <c r="C637">
-        <v>4</v>
-      </c>
-      <c r="D637" t="s">
-        <v>25</v>
-      </c>
-      <c r="E637" s="1">
-        <v>33.136986705476403</v>
-      </c>
-      <c r="F637" s="1">
-        <v>32.630932094647903</v>
-      </c>
-    </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A638" t="s">
-        <v>16</v>
-      </c>
-      <c r="B638" t="s">
-        <v>7</v>
-      </c>
-      <c r="C638">
-        <v>5</v>
-      </c>
-      <c r="D638" t="s">
-        <v>25</v>
-      </c>
-      <c r="E638" s="1">
-        <v>28.425990012226102</v>
-      </c>
-      <c r="F638" s="1">
-        <v>28.392550644951999</v>
-      </c>
-    </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A639" t="s">
-        <v>16</v>
-      </c>
-      <c r="B639" t="s">
-        <v>7</v>
-      </c>
-      <c r="C639">
-        <v>6</v>
-      </c>
-      <c r="D639" t="s">
-        <v>25</v>
-      </c>
-      <c r="E639" s="1">
-        <v>29.4907493719132</v>
-      </c>
-      <c r="F639" s="1">
-        <v>29.533848063526602</v>
-      </c>
-    </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A640" t="s">
-        <v>16</v>
-      </c>
-      <c r="B640" t="s">
-        <v>7</v>
-      </c>
-      <c r="C640">
-        <v>7</v>
-      </c>
-      <c r="D640" t="s">
-        <v>25</v>
-      </c>
-      <c r="E640" s="1">
-        <v>29.704909939280899</v>
-      </c>
-      <c r="F640" s="1">
-        <v>30.357917384956199</v>
-      </c>
-    </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A641" t="s">
-        <v>16</v>
-      </c>
-      <c r="B641" t="s">
-        <v>8</v>
-      </c>
-      <c r="C641">
-        <v>1</v>
-      </c>
-      <c r="D641" t="s">
-        <v>25</v>
-      </c>
-      <c r="E641" s="1">
-        <v>27.168407914522099</v>
-      </c>
-      <c r="F641" s="1">
-        <v>27.6536793442815</v>
-      </c>
-    </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A642" t="s">
-        <v>16</v>
-      </c>
-      <c r="B642" t="s">
-        <v>8</v>
-      </c>
-      <c r="C642">
-        <v>2</v>
-      </c>
-      <c r="D642" t="s">
-        <v>25</v>
-      </c>
-      <c r="E642" s="1">
-        <v>27.609675486490001</v>
-      </c>
-      <c r="F642" s="1">
-        <v>26.964926728312399</v>
-      </c>
-    </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A643" t="s">
-        <v>16</v>
-      </c>
-      <c r="B643" t="s">
-        <v>8</v>
-      </c>
-      <c r="C643">
-        <v>3</v>
-      </c>
-      <c r="D643" t="s">
-        <v>25</v>
-      </c>
-      <c r="E643" s="1">
-        <v>28.144459995911301</v>
-      </c>
-      <c r="F643" s="1">
-        <v>28.764965480241798</v>
-      </c>
-    </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A644" t="s">
-        <v>16</v>
-      </c>
-      <c r="B644" t="s">
-        <v>8</v>
-      </c>
-      <c r="C644">
-        <v>4</v>
-      </c>
-      <c r="D644" t="s">
-        <v>25</v>
-      </c>
-      <c r="E644" s="1">
-        <v>27.182718432696198</v>
-      </c>
-      <c r="F644" s="1">
-        <v>27.336956639467399</v>
-      </c>
-    </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A645" t="s">
-        <v>16</v>
-      </c>
-      <c r="B645" t="s">
-        <v>8</v>
-      </c>
-      <c r="C645">
-        <v>5</v>
-      </c>
-      <c r="D645" t="s">
-        <v>25</v>
-      </c>
-      <c r="E645" s="1">
-        <v>27.918984886755499</v>
-      </c>
-      <c r="F645" s="1">
-        <v>28.173490594127699</v>
-      </c>
-    </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A646" t="s">
-        <v>16</v>
-      </c>
-      <c r="B646" t="s">
-        <v>8</v>
-      </c>
-      <c r="C646">
-        <v>6</v>
-      </c>
-      <c r="D646" t="s">
-        <v>25</v>
-      </c>
-      <c r="E646" s="1">
-        <v>28.891312906224702</v>
-      </c>
-      <c r="F646" s="1">
-        <v>29.148843631370099</v>
-      </c>
-    </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A647" t="s">
-        <v>16</v>
-      </c>
-      <c r="B647" t="s">
-        <v>8</v>
-      </c>
-      <c r="C647">
-        <v>7</v>
-      </c>
-      <c r="D647" t="s">
-        <v>25</v>
-      </c>
-      <c r="E647" s="1">
-        <v>28.011845115892399</v>
-      </c>
-      <c r="F647" s="1">
-        <v>28.185080985237398</v>
-      </c>
-    </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A648" t="s">
-        <v>16</v>
-      </c>
-      <c r="B648" t="s">
-        <v>8</v>
-      </c>
-      <c r="C648">
-        <v>8</v>
-      </c>
-      <c r="D648" t="s">
-        <v>25</v>
-      </c>
-      <c r="E648" s="1">
-        <v>27.6476583637108</v>
-      </c>
-      <c r="F648" s="1">
-        <v>28.067250069473499</v>
-      </c>
-    </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A649" t="s">
-        <v>16</v>
-      </c>
-      <c r="B649" t="s">
-        <v>9</v>
-      </c>
-      <c r="C649">
-        <v>1</v>
-      </c>
-      <c r="D649" t="s">
-        <v>25</v>
-      </c>
-      <c r="E649" s="1">
-        <v>33.102216295024199</v>
-      </c>
-      <c r="F649" s="1">
-        <v>33.104510385428803</v>
-      </c>
-    </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A650" t="s">
-        <v>16</v>
-      </c>
-      <c r="B650" t="s">
-        <v>9</v>
-      </c>
-      <c r="C650">
-        <v>2</v>
-      </c>
-      <c r="D650" t="s">
-        <v>25</v>
-      </c>
-      <c r="E650" s="1">
-        <v>27.813685509001399</v>
-      </c>
-      <c r="F650" s="1">
-        <v>27.786019371039401</v>
-      </c>
-    </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A651" t="s">
-        <v>16</v>
-      </c>
-      <c r="B651" t="s">
-        <v>9</v>
-      </c>
-      <c r="C651">
-        <v>3</v>
-      </c>
-      <c r="D651" t="s">
-        <v>25</v>
-      </c>
-      <c r="E651" s="1">
-        <v>27.0002496869593</v>
-      </c>
-      <c r="F651" s="1">
-        <v>27.048263111997301</v>
-      </c>
-    </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A652" t="s">
-        <v>16</v>
-      </c>
-      <c r="B652" t="s">
-        <v>9</v>
-      </c>
-      <c r="C652">
-        <v>4</v>
-      </c>
-      <c r="D652" t="s">
-        <v>25</v>
-      </c>
-      <c r="E652" s="1">
-        <v>26.914111002612199</v>
-      </c>
-      <c r="F652" s="1">
-        <v>26.680127577512302</v>
-      </c>
-    </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A653" t="s">
-        <v>16</v>
-      </c>
-      <c r="B653" t="s">
-        <v>9</v>
-      </c>
-      <c r="C653">
-        <v>5</v>
-      </c>
-      <c r="D653" t="s">
-        <v>25</v>
-      </c>
-      <c r="E653" s="1">
-        <v>26.219470282299099</v>
-      </c>
-      <c r="F653" s="1">
-        <v>26.061908314495899</v>
-      </c>
-    </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A654" t="s">
-        <v>16</v>
-      </c>
-      <c r="B654" t="s">
-        <v>9</v>
-      </c>
-      <c r="C654">
-        <v>6</v>
-      </c>
-      <c r="D654" t="s">
-        <v>25</v>
-      </c>
-      <c r="E654" s="1">
-        <v>26.713019766875899</v>
-      </c>
-      <c r="F654" s="1">
-        <v>26.591890124942001</v>
-      </c>
-    </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A655" t="s">
-        <v>16</v>
-      </c>
-      <c r="B655" t="s">
-        <v>9</v>
-      </c>
-      <c r="C655">
-        <v>7</v>
-      </c>
-      <c r="D655" t="s">
-        <v>25</v>
-      </c>
-      <c r="E655" s="1">
-        <v>28.341086290718099</v>
-      </c>
-      <c r="F655" s="1">
-        <v>28.133909413643501</v>
-      </c>
-    </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A656" t="s">
-        <v>16</v>
-      </c>
-      <c r="B656" t="s">
-        <v>9</v>
-      </c>
-      <c r="C656">
-        <v>8</v>
-      </c>
-      <c r="D656" t="s">
-        <v>25</v>
-      </c>
-      <c r="E656" s="1">
-        <v>25.840218410083899</v>
-      </c>
-      <c r="F656" s="1">
-        <v>26.463865557737702</v>
-      </c>
-    </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A657" t="s">
-        <v>16</v>
-      </c>
-      <c r="B657" t="s">
-        <v>10</v>
-      </c>
-      <c r="C657">
-        <v>1</v>
-      </c>
-      <c r="D657" t="s">
-        <v>25</v>
-      </c>
-      <c r="E657" s="1">
-        <v>27.398366465647001</v>
-      </c>
-      <c r="F657" s="1">
-        <v>27.102292986943301</v>
-      </c>
-    </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A658" t="s">
-        <v>16</v>
-      </c>
-      <c r="B658" t="s">
-        <v>10</v>
-      </c>
-      <c r="C658">
-        <v>2</v>
-      </c>
-      <c r="D658" t="s">
-        <v>25</v>
-      </c>
-      <c r="E658" s="1">
-        <v>26.850115891102799</v>
-      </c>
-      <c r="F658" s="1">
-        <v>26.795560367619</v>
-      </c>
-    </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A659" t="s">
-        <v>16</v>
-      </c>
-      <c r="B659" t="s">
-        <v>10</v>
-      </c>
-      <c r="C659">
-        <v>3</v>
-      </c>
-      <c r="D659" t="s">
-        <v>25</v>
-      </c>
-      <c r="E659" s="1">
-        <v>26.556454031254798</v>
-      </c>
-      <c r="F659" s="1">
-        <v>26.438626892519199</v>
-      </c>
-    </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A660" t="s">
-        <v>16</v>
-      </c>
-      <c r="B660" t="s">
-        <v>10</v>
-      </c>
-      <c r="C660">
-        <v>4</v>
-      </c>
-      <c r="D660" t="s">
-        <v>25</v>
-      </c>
-      <c r="E660" s="1">
-        <v>26.295859854968199</v>
-      </c>
-      <c r="F660" s="1">
-        <v>26.315415922219699</v>
-      </c>
-    </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A661" t="s">
-        <v>16</v>
-      </c>
-      <c r="B661" t="s">
-        <v>10</v>
-      </c>
-      <c r="C661">
-        <v>5</v>
-      </c>
-      <c r="D661" t="s">
-        <v>25</v>
-      </c>
-      <c r="E661" s="1">
-        <v>26.448558098527801</v>
-      </c>
-      <c r="F661" s="1">
-        <v>26.341777016003</v>
-      </c>
-    </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A662" t="s">
-        <v>16</v>
-      </c>
-      <c r="B662" t="s">
-        <v>10</v>
-      </c>
-      <c r="C662">
-        <v>6</v>
-      </c>
-      <c r="D662" t="s">
-        <v>25</v>
-      </c>
-      <c r="E662" s="1">
-        <v>26.8968557141418</v>
-      </c>
-      <c r="F662" s="1">
-        <v>26.675821102362899</v>
-      </c>
-    </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A663" t="s">
-        <v>16</v>
-      </c>
-      <c r="B663" t="s">
-        <v>10</v>
-      </c>
-      <c r="C663">
-        <v>7</v>
-      </c>
-      <c r="D663" t="s">
-        <v>25</v>
-      </c>
-      <c r="E663" s="1">
-        <v>26.190511241868499</v>
-      </c>
-      <c r="F663" s="1">
-        <v>26.071947071713101</v>
-      </c>
-    </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A664" t="s">
-        <v>16</v>
-      </c>
-      <c r="B664" t="s">
-        <v>10</v>
-      </c>
-      <c r="C664">
-        <v>8</v>
-      </c>
-      <c r="D664" t="s">
-        <v>25</v>
-      </c>
-      <c r="E664" s="1">
-        <v>26.186975051831801</v>
-      </c>
-      <c r="F664" s="1">
-        <v>26.1776042433413</v>
+        <v>21.79</v>
       </c>
     </row>
   </sheetData>
